--- a/data/2025/41-vrancea/174744-focsani/budget_file.xlsx
+++ b/data/2025/41-vrancea/174744-focsani/budget_file.xlsx
@@ -569,22 +569,22 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>Sectiunea de dezvoltare</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>transferuri</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>inst_integral_venituri_proprii</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Sectiunea de functionare</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Sectiunea de dezvoltare</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
@@ -624,13 +624,13 @@
         <v>3.673</v>
       </c>
       <c r="R2" s="3" t="n"/>
-      <c r="S2" s="3" t="n">
+      <c r="S2" s="3" t="n"/>
+      <c r="T2" s="3" t="n">
         <v>-21.968</v>
       </c>
-      <c r="T2" s="3" t="n">
+      <c r="U2" s="3" t="n">
         <v>30.213</v>
       </c>
-      <c r="U2" s="3" t="n"/>
       <c r="V2" s="3" t="n"/>
       <c r="W2" t="inlineStr">
         <is>
@@ -663,10 +663,10 @@
       <c r="Q3" s="3" t="n"/>
       <c r="R3" s="3" t="n"/>
       <c r="S3" s="3" t="n"/>
-      <c r="T3" s="3" t="n">
+      <c r="T3" s="3" t="n"/>
+      <c r="U3" s="3" t="n">
         <v>8.128</v>
       </c>
-      <c r="U3" s="3" t="n"/>
       <c r="V3" s="3" t="n"/>
       <c r="W3" t="inlineStr">
         <is>
@@ -799,10 +799,10 @@
       <c r="Q7" s="3" t="n"/>
       <c r="R7" s="3" t="n"/>
       <c r="S7" s="3" t="n"/>
-      <c r="T7" s="3" t="n">
+      <c r="T7" s="3" t="n"/>
+      <c r="U7" s="3" t="n">
         <v>8.128</v>
       </c>
-      <c r="U7" s="3" t="n"/>
       <c r="V7" s="3" t="n"/>
       <c r="W7" t="inlineStr">
         <is>
@@ -835,10 +835,10 @@
       <c r="Q8" s="3" t="n"/>
       <c r="R8" s="3" t="n"/>
       <c r="S8" s="3" t="n"/>
-      <c r="T8" s="3" t="n">
+      <c r="T8" s="3" t="n"/>
+      <c r="U8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="U8" s="3" t="n"/>
       <c r="V8" s="3" t="n"/>
       <c r="W8" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
       <c r="Q17" s="3" t="n"/>
       <c r="R17" s="3" t="n"/>
       <c r="S17" s="3" t="n"/>
-      <c r="T17" s="3" t="n">
+      <c r="T17" s="3" t="n"/>
+      <c r="U17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="U17" s="3" t="n"/>
       <c r="V17" s="3" t="n"/>
       <c r="W17" t="inlineStr">
         <is>
@@ -1448,13 +1448,13 @@
       <c r="P26" s="3" t="n"/>
       <c r="Q26" s="3" t="n"/>
       <c r="R26" s="3" t="n"/>
-      <c r="S26" s="3" t="n">
+      <c r="S26" s="3" t="n"/>
+      <c r="T26" s="3" t="n">
         <v>-21.968</v>
       </c>
-      <c r="T26" s="3" t="n">
+      <c r="U26" s="3" t="n">
         <v>21.968</v>
       </c>
-      <c r="U26" s="3" t="n"/>
       <c r="V26" s="3" t="n"/>
       <c r="W26" t="inlineStr">
         <is>
@@ -1524,10 +1524,10 @@
       <c r="Q28" s="3" t="n"/>
       <c r="R28" s="3" t="n"/>
       <c r="S28" s="3" t="n"/>
-      <c r="T28" s="3" t="n">
+      <c r="T28" s="3" t="n"/>
+      <c r="U28" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="U28" s="3" t="n"/>
       <c r="V28" s="3" t="n"/>
       <c r="W28" t="inlineStr">
         <is>
@@ -1561,13 +1561,13 @@
         <v>3.673</v>
       </c>
       <c r="R29" s="3" t="n"/>
-      <c r="S29" s="3" t="n">
+      <c r="S29" s="3" t="n"/>
+      <c r="T29" s="3" t="n">
         <v>-21.968</v>
       </c>
-      <c r="T29" s="3" t="n">
+      <c r="U29" s="3" t="n">
         <v>30.213</v>
       </c>
-      <c r="U29" s="3" t="n"/>
       <c r="V29" s="3" t="n"/>
       <c r="W29" t="inlineStr">
         <is>
@@ -1639,13 +1639,13 @@
       </c>
       <c r="Q31" s="3" t="n"/>
       <c r="R31" s="3" t="n"/>
-      <c r="S31" s="3" t="n">
+      <c r="S31" s="3" t="n"/>
+      <c r="T31" s="3" t="n">
         <v>-3.838</v>
       </c>
-      <c r="T31" s="3" t="n">
+      <c r="U31" s="3" t="n">
         <v>4.043</v>
       </c>
-      <c r="U31" s="3" t="n"/>
       <c r="V31" s="3" t="n"/>
       <c r="W31" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
       <c r="Q35" s="3" t="n"/>
       <c r="R35" s="3" t="n"/>
       <c r="S35" s="3" t="n"/>
-      <c r="T35" s="3" t="n">
+      <c r="T35" s="3" t="n"/>
+      <c r="U35" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="U35" s="3" t="n"/>
       <c r="V35" s="3" t="n"/>
       <c r="W35" t="inlineStr">
         <is>
@@ -1830,13 +1830,13 @@
       </c>
       <c r="Q36" s="3" t="n"/>
       <c r="R36" s="3" t="n"/>
-      <c r="S36" s="3" t="n">
+      <c r="S36" s="3" t="n"/>
+      <c r="T36" s="3" t="n">
         <v>-18.13</v>
       </c>
-      <c r="T36" s="3" t="n">
+      <c r="U36" s="3" t="n">
         <v>18.97</v>
       </c>
-      <c r="U36" s="3" t="n"/>
       <c r="V36" s="3" t="n"/>
       <c r="W36" t="inlineStr">
         <is>
@@ -2096,13 +2096,13 @@
         <v>3.673</v>
       </c>
       <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n">
+      <c r="S43" s="3" t="n"/>
+      <c r="T43" s="3" t="n">
         <v>-21.968</v>
       </c>
-      <c r="T43" s="3" t="n">
+      <c r="U43" s="3" t="n">
         <v>30.213</v>
       </c>
-      <c r="U43" s="3" t="n"/>
       <c r="V43" s="3" t="n"/>
       <c r="W43" t="inlineStr">
         <is>
@@ -2136,13 +2136,13 @@
         <v>0</v>
       </c>
       <c r="R44" s="3" t="n"/>
-      <c r="S44" s="3" t="n">
+      <c r="S44" s="3" t="n"/>
+      <c r="T44" s="3" t="n">
         <v>-21.875</v>
       </c>
-      <c r="T44" s="3" t="n">
+      <c r="U44" s="3" t="n">
         <v>30.12</v>
       </c>
-      <c r="U44" s="3" t="n"/>
       <c r="V44" s="3" t="n"/>
       <c r="W44" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
       <c r="Q45" s="3" t="n"/>
       <c r="R45" s="3" t="n"/>
       <c r="S45" s="3" t="n"/>
-      <c r="T45" s="3" t="n">
+      <c r="T45" s="3" t="n"/>
+      <c r="U45" s="3" t="n">
         <v>10.076</v>
       </c>
-      <c r="U45" s="3" t="n"/>
       <c r="V45" s="3" t="n"/>
       <c r="W45" t="inlineStr">
         <is>
@@ -2217,10 +2217,10 @@
       <c r="Q46" s="3" t="n"/>
       <c r="R46" s="3" t="n"/>
       <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n">
+      <c r="T46" s="3" t="n"/>
+      <c r="U46" s="3" t="n">
         <v>20.01</v>
       </c>
-      <c r="U46" s="3" t="n"/>
       <c r="V46" s="3" t="n"/>
       <c r="W46" t="inlineStr">
         <is>
@@ -2366,10 +2366,10 @@
       </c>
       <c r="Q50" s="3" t="n"/>
       <c r="R50" s="3" t="n"/>
-      <c r="S50" s="3" t="n">
+      <c r="S50" s="3" t="n"/>
+      <c r="T50" s="3" t="n">
         <v>-21.875</v>
       </c>
-      <c r="T50" s="3" t="n"/>
       <c r="U50" s="3" t="n"/>
       <c r="V50" s="3" t="n"/>
       <c r="W50" t="inlineStr">
@@ -2443,10 +2443,10 @@
       <c r="Q52" s="3" t="n"/>
       <c r="R52" s="3" t="n"/>
       <c r="S52" s="3" t="n"/>
-      <c r="T52" s="3" t="n">
+      <c r="T52" s="3" t="n"/>
+      <c r="U52" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="U52" s="3" t="n"/>
       <c r="V52" s="3" t="n"/>
       <c r="W52" t="inlineStr">
         <is>
@@ -2554,13 +2554,13 @@
         <v>3.673</v>
       </c>
       <c r="R55" s="3" t="n"/>
-      <c r="S55" s="3" t="n">
+      <c r="S55" s="3" t="n"/>
+      <c r="T55" s="3" t="n">
         <v>-93</v>
       </c>
-      <c r="T55" s="3" t="n">
+      <c r="U55" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="U55" s="3" t="n"/>
       <c r="V55" s="3" t="n"/>
       <c r="W55" t="inlineStr">
         <is>
@@ -2595,10 +2595,10 @@
       </c>
       <c r="Q56" s="3" t="n"/>
       <c r="R56" s="3" t="n"/>
-      <c r="S56" s="3" t="n">
+      <c r="S56" s="3" t="n"/>
+      <c r="T56" s="3" t="n">
         <v>-93</v>
       </c>
-      <c r="T56" s="3" t="n"/>
       <c r="U56" s="3" t="n"/>
       <c r="V56" s="3" t="n"/>
       <c r="W56" t="inlineStr">
@@ -2710,10 +2710,10 @@
       </c>
       <c r="R59" s="3" t="n"/>
       <c r="S59" s="3" t="n"/>
-      <c r="T59" s="3" t="n">
+      <c r="T59" s="3" t="n"/>
+      <c r="U59" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="U59" s="3" t="n"/>
       <c r="V59" s="3" t="n"/>
       <c r="W59" t="inlineStr">
         <is>
@@ -14040,13 +14040,13 @@
       <c r="R309" s="3" t="n">
         <v>567.7380000000001</v>
       </c>
-      <c r="S309" s="3" t="n"/>
+      <c r="S309" s="3" t="n">
+        <v>297.284</v>
+      </c>
       <c r="T309" s="3" t="n"/>
-      <c r="U309" s="3" t="n">
+      <c r="U309" s="3" t="n"/>
+      <c r="V309" s="3" t="n">
         <v>270.454</v>
-      </c>
-      <c r="V309" s="3" t="n">
-        <v>297.284</v>
       </c>
       <c r="W309" t="inlineStr">
         <is>
@@ -14078,13 +14078,13 @@
       <c r="R310" s="3" t="n">
         <v>405.235</v>
       </c>
-      <c r="S310" s="3" t="n"/>
+      <c r="S310" s="3" t="n">
+        <v>294.109</v>
+      </c>
       <c r="T310" s="3" t="n"/>
-      <c r="U310" s="3" t="n">
+      <c r="U310" s="3" t="n"/>
+      <c r="V310" s="3" t="n">
         <v>111.126</v>
-      </c>
-      <c r="V310" s="3" t="n">
-        <v>294.109</v>
       </c>
       <c r="W310" t="inlineStr">
         <is>
@@ -14125,13 +14125,13 @@
       <c r="R311" s="3" t="n">
         <v>46.35</v>
       </c>
-      <c r="S311" s="3" t="n"/>
+      <c r="S311" s="3" t="n">
+        <v>9.835000000000001</v>
+      </c>
       <c r="T311" s="3" t="n"/>
-      <c r="U311" s="3" t="n">
+      <c r="U311" s="3" t="n"/>
+      <c r="V311" s="3" t="n">
         <v>36.515</v>
-      </c>
-      <c r="V311" s="3" t="n">
-        <v>9.835000000000001</v>
       </c>
       <c r="W311" t="inlineStr">
         <is>
@@ -14165,10 +14165,10 @@
       </c>
       <c r="S312" s="3" t="n"/>
       <c r="T312" s="3" t="n"/>
-      <c r="U312" s="3" t="n">
+      <c r="U312" s="3" t="n"/>
+      <c r="V312" s="3" t="n">
         <v>29.915</v>
       </c>
-      <c r="V312" s="3" t="n"/>
       <c r="W312" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -14201,10 +14201,10 @@
       </c>
       <c r="S313" s="3" t="n"/>
       <c r="T313" s="3" t="n"/>
-      <c r="U313" s="3" t="n">
+      <c r="U313" s="3" t="n"/>
+      <c r="V313" s="3" t="n">
         <v>6.364</v>
       </c>
-      <c r="V313" s="3" t="n"/>
       <c r="W313" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -14237,10 +14237,10 @@
       </c>
       <c r="S314" s="3" t="n"/>
       <c r="T314" s="3" t="n"/>
-      <c r="U314" s="3" t="n">
+      <c r="U314" s="3" t="n"/>
+      <c r="V314" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="V314" s="3" t="n"/>
       <c r="W314" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -14273,10 +14273,10 @@
       </c>
       <c r="S315" s="3" t="n"/>
       <c r="T315" s="3" t="n"/>
-      <c r="U315" s="3" t="n">
+      <c r="U315" s="3" t="n"/>
+      <c r="V315" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="V315" s="3" t="n"/>
       <c r="W315" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -14341,12 +14341,12 @@
       <c r="R317" s="3" t="n">
         <v>9.696999999999999</v>
       </c>
-      <c r="S317" s="3" t="n"/>
+      <c r="S317" s="3" t="n">
+        <v>9.696999999999999</v>
+      </c>
       <c r="T317" s="3" t="n"/>
       <c r="U317" s="3" t="n"/>
-      <c r="V317" s="3" t="n">
-        <v>9.696999999999999</v>
-      </c>
+      <c r="V317" s="3" t="n"/>
       <c r="W317" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -14377,12 +14377,12 @@
       <c r="R318" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="S318" s="3" t="n"/>
+      <c r="S318" s="3" t="n">
+        <v>138</v>
+      </c>
       <c r="T318" s="3" t="n"/>
       <c r="U318" s="3" t="n"/>
-      <c r="V318" s="3" t="n">
-        <v>138</v>
-      </c>
+      <c r="V318" s="3" t="n"/>
       <c r="W318" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -14422,13 +14422,13 @@
       <c r="R319" s="3" t="n">
         <v>4.873</v>
       </c>
-      <c r="S319" s="3" t="n"/>
+      <c r="S319" s="3" t="n">
+        <v>63</v>
+      </c>
       <c r="T319" s="3" t="n"/>
-      <c r="U319" s="3" t="n">
+      <c r="U319" s="3" t="n"/>
+      <c r="V319" s="3" t="n">
         <v>4.81</v>
-      </c>
-      <c r="V319" s="3" t="n">
-        <v>63</v>
       </c>
       <c r="W319" t="inlineStr">
         <is>
@@ -14460,13 +14460,13 @@
       <c r="R320" s="3" t="n">
         <v>3.838</v>
       </c>
-      <c r="S320" s="3" t="n"/>
+      <c r="S320" s="3" t="n">
+        <v>63</v>
+      </c>
       <c r="T320" s="3" t="n"/>
-      <c r="U320" s="3" t="n">
+      <c r="U320" s="3" t="n"/>
+      <c r="V320" s="3" t="n">
         <v>3.775</v>
-      </c>
-      <c r="V320" s="3" t="n">
-        <v>63</v>
       </c>
       <c r="W320" t="inlineStr">
         <is>
@@ -14500,10 +14500,10 @@
       </c>
       <c r="S321" s="3" t="n"/>
       <c r="T321" s="3" t="n"/>
-      <c r="U321" s="3" t="n">
+      <c r="U321" s="3" t="n"/>
+      <c r="V321" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="V321" s="3" t="n"/>
       <c r="W321" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -14536,10 +14536,10 @@
       </c>
       <c r="S322" s="3" t="n"/>
       <c r="T322" s="3" t="n"/>
-      <c r="U322" s="3" t="n">
+      <c r="U322" s="3" t="n"/>
+      <c r="V322" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="V322" s="3" t="n"/>
       <c r="W322" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -14581,13 +14581,13 @@
       <c r="R323" s="7" t="n">
         <v>9.33</v>
       </c>
-      <c r="S323" s="7" t="n"/>
+      <c r="S323" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="T323" s="7" t="n"/>
-      <c r="U323" s="7" t="n">
+      <c r="U323" s="7" t="n"/>
+      <c r="V323" s="7" t="n">
         <v>9.33</v>
-      </c>
-      <c r="V323" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="W323" s="6" t="inlineStr">
         <is>
@@ -14626,10 +14626,10 @@
       </c>
       <c r="S324" s="3" t="n"/>
       <c r="T324" s="3" t="n"/>
-      <c r="U324" s="3" t="n">
+      <c r="U324" s="3" t="n"/>
+      <c r="V324" s="3" t="n">
         <v>9.33</v>
       </c>
-      <c r="V324" s="3" t="n"/>
       <c r="W324" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -14703,13 +14703,13 @@
       <c r="R326" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="S326" s="3" t="n"/>
+      <c r="S326" s="3" t="n">
+        <v>70</v>
+      </c>
       <c r="T326" s="3" t="n"/>
-      <c r="U326" s="3" t="n">
+      <c r="U326" s="3" t="n"/>
+      <c r="V326" s="3" t="n">
         <v>180</v>
-      </c>
-      <c r="V326" s="3" t="n">
-        <v>70</v>
       </c>
       <c r="W326" t="inlineStr">
         <is>
@@ -14743,10 +14743,10 @@
       </c>
       <c r="S327" s="3" t="n"/>
       <c r="T327" s="3" t="n"/>
-      <c r="U327" s="3" t="n">
+      <c r="U327" s="3" t="n"/>
+      <c r="V327" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="V327" s="3" t="n"/>
       <c r="W327" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -14777,12 +14777,12 @@
       <c r="R328" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="S328" s="3" t="n"/>
+      <c r="S328" s="3" t="n">
+        <v>70</v>
+      </c>
       <c r="T328" s="3" t="n"/>
       <c r="U328" s="3" t="n"/>
-      <c r="V328" s="3" t="n">
-        <v>70</v>
-      </c>
+      <c r="V328" s="3" t="n"/>
       <c r="W328" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -14822,13 +14822,13 @@
       <c r="R329" s="3" t="n">
         <v>16.671</v>
       </c>
-      <c r="S329" s="3" t="n"/>
+      <c r="S329" s="3" t="n">
+        <v>15.82</v>
+      </c>
       <c r="T329" s="3" t="n"/>
-      <c r="U329" s="3" t="n">
+      <c r="U329" s="3" t="n"/>
+      <c r="V329" s="3" t="n">
         <v>851</v>
-      </c>
-      <c r="V329" s="3" t="n">
-        <v>15.82</v>
       </c>
       <c r="W329" t="inlineStr">
         <is>
@@ -14862,10 +14862,10 @@
       </c>
       <c r="S330" s="3" t="n"/>
       <c r="T330" s="3" t="n"/>
-      <c r="U330" s="3" t="n">
+      <c r="U330" s="3" t="n"/>
+      <c r="V330" s="3" t="n">
         <v>851</v>
       </c>
-      <c r="V330" s="3" t="n"/>
       <c r="W330" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -14896,12 +14896,12 @@
       <c r="R331" s="3" t="n">
         <v>980</v>
       </c>
-      <c r="S331" s="3" t="n"/>
+      <c r="S331" s="3" t="n">
+        <v>980</v>
+      </c>
       <c r="T331" s="3" t="n"/>
       <c r="U331" s="3" t="n"/>
-      <c r="V331" s="3" t="n">
-        <v>980</v>
-      </c>
+      <c r="V331" s="3" t="n"/>
       <c r="W331" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -14932,12 +14932,12 @@
       <c r="R332" s="3" t="n">
         <v>2.17</v>
       </c>
-      <c r="S332" s="3" t="n"/>
+      <c r="S332" s="3" t="n">
+        <v>2.17</v>
+      </c>
       <c r="T332" s="3" t="n"/>
       <c r="U332" s="3" t="n"/>
-      <c r="V332" s="3" t="n">
-        <v>2.17</v>
-      </c>
+      <c r="V332" s="3" t="n"/>
       <c r="W332" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -14968,12 +14968,12 @@
       <c r="R333" s="3" t="n">
         <v>12.67</v>
       </c>
-      <c r="S333" s="3" t="n"/>
+      <c r="S333" s="3" t="n">
+        <v>12.67</v>
+      </c>
       <c r="T333" s="3" t="n"/>
       <c r="U333" s="3" t="n"/>
-      <c r="V333" s="3" t="n">
-        <v>12.67</v>
-      </c>
+      <c r="V333" s="3" t="n"/>
       <c r="W333" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -15013,11 +15013,11 @@
       <c r="R334" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S334" s="3" t="n"/>
+      <c r="S334" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="T334" s="3" t="n"/>
-      <c r="U334" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="U334" s="3" t="n"/>
       <c r="V334" s="3" t="n">
         <v>0</v>
       </c>
@@ -15094,13 +15094,13 @@
       <c r="R336" s="3" t="n">
         <v>22.952</v>
       </c>
-      <c r="S336" s="3" t="n"/>
+      <c r="S336" s="3" t="n">
+        <v>3.182</v>
+      </c>
       <c r="T336" s="3" t="n"/>
-      <c r="U336" s="3" t="n">
+      <c r="U336" s="3" t="n"/>
+      <c r="V336" s="3" t="n">
         <v>19.77</v>
-      </c>
-      <c r="V336" s="3" t="n">
-        <v>3.182</v>
       </c>
       <c r="W336" t="inlineStr">
         <is>
@@ -15134,10 +15134,10 @@
       </c>
       <c r="S337" s="3" t="n"/>
       <c r="T337" s="3" t="n"/>
-      <c r="U337" s="3" t="n">
+      <c r="U337" s="3" t="n"/>
+      <c r="V337" s="3" t="n">
         <v>650</v>
       </c>
-      <c r="V337" s="3" t="n"/>
       <c r="W337" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -15170,10 +15170,10 @@
       </c>
       <c r="S338" s="3" t="n"/>
       <c r="T338" s="3" t="n"/>
-      <c r="U338" s="3" t="n">
+      <c r="U338" s="3" t="n"/>
+      <c r="V338" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V338" s="3" t="n"/>
       <c r="W338" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -15206,10 +15206,10 @@
       </c>
       <c r="S339" s="3" t="n"/>
       <c r="T339" s="3" t="n"/>
-      <c r="U339" s="3" t="n">
+      <c r="U339" s="3" t="n"/>
+      <c r="V339" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="V339" s="3" t="n"/>
       <c r="W339" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -15240,13 +15240,13 @@
       <c r="R340" s="3" t="n">
         <v>6.43</v>
       </c>
-      <c r="S340" s="3" t="n"/>
+      <c r="S340" s="3" t="n">
+        <v>30</v>
+      </c>
       <c r="T340" s="3" t="n"/>
-      <c r="U340" s="3" t="n">
+      <c r="U340" s="3" t="n"/>
+      <c r="V340" s="3" t="n">
         <v>6.4</v>
-      </c>
-      <c r="V340" s="3" t="n">
-        <v>30</v>
       </c>
       <c r="W340" t="inlineStr">
         <is>
@@ -15280,10 +15280,10 @@
       </c>
       <c r="S341" s="3" t="n"/>
       <c r="T341" s="3" t="n"/>
-      <c r="U341" s="3" t="n">
+      <c r="U341" s="3" t="n"/>
+      <c r="V341" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="V341" s="3" t="n"/>
       <c r="W341" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -15314,12 +15314,12 @@
       <c r="R342" s="3" t="n">
         <v>176</v>
       </c>
-      <c r="S342" s="3" t="n"/>
+      <c r="S342" s="3" t="n">
+        <v>176</v>
+      </c>
       <c r="T342" s="3" t="n"/>
       <c r="U342" s="3" t="n"/>
-      <c r="V342" s="3" t="n">
-        <v>176</v>
-      </c>
+      <c r="V342" s="3" t="n"/>
       <c r="W342" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -15350,12 +15350,12 @@
       <c r="R343" s="3" t="n">
         <v>2.191</v>
       </c>
-      <c r="S343" s="3" t="n"/>
+      <c r="S343" s="3" t="n">
+        <v>2.191</v>
+      </c>
       <c r="T343" s="3" t="n"/>
       <c r="U343" s="3" t="n"/>
-      <c r="V343" s="3" t="n">
-        <v>2.191</v>
-      </c>
+      <c r="V343" s="3" t="n"/>
       <c r="W343" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -15386,12 +15386,12 @@
       <c r="R344" s="3" t="n">
         <v>785</v>
       </c>
-      <c r="S344" s="3" t="n"/>
+      <c r="S344" s="3" t="n">
+        <v>785</v>
+      </c>
       <c r="T344" s="3" t="n"/>
       <c r="U344" s="3" t="n"/>
-      <c r="V344" s="3" t="n">
-        <v>785</v>
-      </c>
+      <c r="V344" s="3" t="n"/>
       <c r="W344" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -15431,13 +15431,13 @@
       <c r="R345" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="S345" s="3" t="n"/>
+      <c r="S345" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="T345" s="3" t="n"/>
-      <c r="U345" s="3" t="n">
+      <c r="U345" s="3" t="n"/>
+      <c r="V345" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="V345" s="3" t="n">
-        <v>5</v>
       </c>
       <c r="W345" t="inlineStr">
         <is>
@@ -15503,12 +15503,12 @@
       <c r="R347" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="S347" s="3" t="n"/>
+      <c r="S347" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="T347" s="3" t="n"/>
       <c r="U347" s="3" t="n"/>
-      <c r="V347" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="V347" s="3" t="n"/>
       <c r="W347" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -15582,13 +15582,13 @@
       <c r="R349" s="3" t="n">
         <v>52.208</v>
       </c>
-      <c r="S349" s="3" t="n"/>
+      <c r="S349" s="3" t="n">
+        <v>42.023</v>
+      </c>
       <c r="T349" s="3" t="n"/>
-      <c r="U349" s="3" t="n">
+      <c r="U349" s="3" t="n"/>
+      <c r="V349" s="3" t="n">
         <v>10.185</v>
-      </c>
-      <c r="V349" s="3" t="n">
-        <v>42.023</v>
       </c>
       <c r="W349" t="inlineStr">
         <is>
@@ -15622,10 +15622,10 @@
       </c>
       <c r="S350" s="3" t="n"/>
       <c r="T350" s="3" t="n"/>
-      <c r="U350" s="3" t="n">
+      <c r="U350" s="3" t="n"/>
+      <c r="V350" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V350" s="3" t="n"/>
       <c r="W350" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -15658,10 +15658,10 @@
       </c>
       <c r="S351" s="3" t="n"/>
       <c r="T351" s="3" t="n"/>
-      <c r="U351" s="3" t="n">
+      <c r="U351" s="3" t="n"/>
+      <c r="V351" s="3" t="n">
         <v>810</v>
       </c>
-      <c r="V351" s="3" t="n"/>
       <c r="W351" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -15694,10 +15694,10 @@
       </c>
       <c r="S352" s="3" t="n"/>
       <c r="T352" s="3" t="n"/>
-      <c r="U352" s="3" t="n">
+      <c r="U352" s="3" t="n"/>
+      <c r="V352" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="V352" s="3" t="n"/>
       <c r="W352" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -15730,10 +15730,10 @@
       </c>
       <c r="S353" s="3" t="n"/>
       <c r="T353" s="3" t="n"/>
-      <c r="U353" s="3" t="n">
+      <c r="U353" s="3" t="n"/>
+      <c r="V353" s="3" t="n">
         <v>675</v>
       </c>
-      <c r="V353" s="3" t="n"/>
       <c r="W353" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -15764,12 +15764,12 @@
       <c r="R354" s="3" t="n">
         <v>28.136</v>
       </c>
-      <c r="S354" s="3" t="n"/>
+      <c r="S354" s="3" t="n">
+        <v>28.136</v>
+      </c>
       <c r="T354" s="3" t="n"/>
       <c r="U354" s="3" t="n"/>
-      <c r="V354" s="3" t="n">
-        <v>28.136</v>
-      </c>
+      <c r="V354" s="3" t="n"/>
       <c r="W354" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -15800,12 +15800,12 @@
       <c r="R355" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="S355" s="3" t="n"/>
+      <c r="S355" s="3" t="n">
+        <v>106</v>
+      </c>
       <c r="T355" s="3" t="n"/>
       <c r="U355" s="3" t="n"/>
-      <c r="V355" s="3" t="n">
-        <v>106</v>
-      </c>
+      <c r="V355" s="3" t="n"/>
       <c r="W355" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -15836,12 +15836,12 @@
       <c r="R356" s="3" t="n">
         <v>13.781</v>
       </c>
-      <c r="S356" s="3" t="n"/>
+      <c r="S356" s="3" t="n">
+        <v>13.781</v>
+      </c>
       <c r="T356" s="3" t="n"/>
       <c r="U356" s="3" t="n"/>
-      <c r="V356" s="3" t="n">
-        <v>13.781</v>
-      </c>
+      <c r="V356" s="3" t="n"/>
       <c r="W356" t="inlineStr">
         <is>
           <t>llm:gemini-3.6-flash</t>
@@ -26432,7 +26432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K379"/>
+  <dimension ref="A1:K377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29252,13 +29252,17 @@
       </c>
     </row>
     <row r="140">
-      <c r="C140" s="2" t="inlineStr"/>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Monitor wide (1 buc)</t>
+        </is>
+      </c>
       <c r="E140" t="n">
         <v>23</v>
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" s="3" t="n">
-        <v>15003</v>
+        <v>3</v>
       </c>
       <c r="H140" s="3" t="n"/>
       <c r="I140" s="3" t="n"/>
@@ -29269,20 +29273,16 @@
       </c>
     </row>
     <row r="141">
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Monitor wide (1 buc)</t>
-        </is>
-      </c>
+      <c r="C141" s="2" t="inlineStr"/>
       <c r="E141" t="n">
         <v>23</v>
       </c>
       <c r="F141" t="inlineStr"/>
-      <c r="G141" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="G141" s="3" t="n"/>
       <c r="H141" s="3" t="n"/>
-      <c r="I141" s="3" t="n"/>
+      <c r="I141" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J141" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -29290,16 +29290,20 @@
       </c>
     </row>
     <row r="142">
-      <c r="C142" s="2" t="inlineStr"/>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Router program-Evidenta persoanelor</t>
+        </is>
+      </c>
       <c r="E142" t="n">
         <v>23</v>
       </c>
       <c r="F142" t="inlineStr"/>
-      <c r="G142" s="3" t="n"/>
+      <c r="G142" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="H142" s="3" t="n"/>
-      <c r="I142" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I142" s="3" t="n"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -29309,18 +29313,20 @@
     <row r="143">
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Router program-Evidenta persoanelor</t>
+          <t>Alte servicii publice generale</t>
         </is>
       </c>
       <c r="E143" t="n">
         <v>23</v>
       </c>
       <c r="F143" t="inlineStr"/>
-      <c r="G143" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H143" s="3" t="n"/>
-      <c r="I143" s="3" t="n"/>
+      <c r="G143" s="3" t="n"/>
+      <c r="H143" s="3" t="n">
+        <v>54.02</v>
+      </c>
+      <c r="I143" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J143" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -29328,22 +29334,16 @@
       </c>
     </row>
     <row r="144">
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Alte servicii publice generale</t>
-        </is>
-      </c>
+      <c r="C144" s="2" t="inlineStr"/>
       <c r="E144" t="n">
         <v>23</v>
       </c>
       <c r="F144" t="inlineStr"/>
-      <c r="G144" s="3" t="n"/>
-      <c r="H144" s="3" t="n">
-        <v>54.02</v>
-      </c>
-      <c r="I144" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="G144" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H144" s="3" t="n"/>
+      <c r="I144" s="3" t="n"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -29351,7 +29351,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="C145" s="2" t="inlineStr"/>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>DIRECTIA DE DEZVOLTARE SERVICII PUBLICE</t>
+        </is>
+      </c>
       <c r="E145" t="n">
         <v>23</v>
       </c>
@@ -29360,7 +29364,9 @@
         <v>45</v>
       </c>
       <c r="H145" s="3" t="n"/>
-      <c r="I145" s="3" t="n"/>
+      <c r="I145" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J145" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -29370,7 +29376,7 @@
     <row r="146">
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>DIRECTIA DE DEZVOLTARE SERVICII PUBLICE</t>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -29381,9 +29387,7 @@
         <v>45</v>
       </c>
       <c r="H146" s="3" t="n"/>
-      <c r="I146" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I146" s="3" t="n"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -29393,7 +29397,7 @@
     <row r="147">
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
+          <t>_Actualizare prin refacere a ortofotoplanului Cimitirului</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -29404,7 +29408,9 @@
         <v>45</v>
       </c>
       <c r="H147" s="3" t="n"/>
-      <c r="I147" s="3" t="n"/>
+      <c r="I147" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J147" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -29414,7 +29420,7 @@
     <row r="148">
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>_Actualizare prin refacere a ortofotoplanului Cimitirului</t>
+          <t>Sudic si extinderea capacitatii softului pentru gestionarea Cimitirului Sudic si Nordic</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -29425,9 +29431,7 @@
         <v>45</v>
       </c>
       <c r="H148" s="3" t="n"/>
-      <c r="I148" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I148" s="3" t="n"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -29435,17 +29439,13 @@
       </c>
     </row>
     <row r="149">
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Sudic si extinderea capacitatii softului pentru gestionarea Cimitirului Sudic si Nordic</t>
-        </is>
-      </c>
+      <c r="C149" s="2" t="inlineStr"/>
       <c r="E149" t="n">
         <v>23</v>
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" s="3" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="H149" s="3" t="n"/>
       <c r="I149" s="3" t="n"/>
@@ -29456,7 +29456,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="C150" s="2" t="inlineStr"/>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>61.02 Ordine publică si siguranța națională</t>
+        </is>
+      </c>
       <c r="E150" t="n">
         <v>23</v>
       </c>
@@ -29475,7 +29479,7 @@
     <row r="151">
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>61.02 Ordine publică si siguranța națională</t>
+          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI</t>
         </is>
       </c>
       <c r="E151" t="n">
@@ -29494,11 +29498,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI</t>
-        </is>
-      </c>
+      <c r="C152" s="2" t="inlineStr"/>
       <c r="E152" t="n">
         <v>23</v>
       </c>
@@ -29515,7 +29515,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="C153" s="2" t="inlineStr"/>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
+        </is>
+      </c>
       <c r="E153" t="n">
         <v>23</v>
       </c>
@@ -29532,11 +29536,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
-        </is>
-      </c>
+      <c r="C154" s="2" t="inlineStr"/>
       <c r="E154" t="n">
         <v>23</v>
       </c>
@@ -29553,7 +29553,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="C155" s="2" t="inlineStr"/>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Documentatie reparatii capitale si modernizare adaposturi</t>
+        </is>
+      </c>
       <c r="E155" t="n">
         <v>23</v>
       </c>
@@ -29562,7 +29566,9 @@
         <v>70</v>
       </c>
       <c r="H155" s="3" t="n"/>
-      <c r="I155" s="3" t="n"/>
+      <c r="I155" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J155" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -29572,7 +29578,7 @@
     <row r="156">
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Documentatie reparatii capitale si modernizare adaposturi</t>
+          <t>de protectie civila</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -29583,9 +29589,7 @@
         <v>70</v>
       </c>
       <c r="H156" s="3" t="n"/>
-      <c r="I156" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I156" s="3" t="n"/>
       <c r="J156" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -29595,17 +29599,19 @@
     <row r="157">
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>de protectie civila</t>
+          <t>îNVĂTĂMÂNT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="H157" s="3" t="n"/>
+        <v>1431.74</v>
+      </c>
+      <c r="H157" s="3" t="n">
+        <v>65.02</v>
+      </c>
       <c r="I157" s="3" t="n"/>
       <c r="J157" t="inlineStr">
         <is>
@@ -29614,11 +29620,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>îNVĂTĂMÂNT</t>
-        </is>
-      </c>
+      <c r="C158" s="2" t="inlineStr"/>
       <c r="E158" t="n">
         <v>24</v>
       </c>
@@ -29626,9 +29628,7 @@
       <c r="G158" s="3" t="n">
         <v>1431.74</v>
       </c>
-      <c r="H158" s="3" t="n">
-        <v>65.02</v>
-      </c>
+      <c r="H158" s="3" t="n"/>
       <c r="I158" s="3" t="n"/>
       <c r="J158" t="inlineStr">
         <is>
@@ -29637,13 +29637,17 @@
       </c>
     </row>
     <row r="159">
-      <c r="C159" s="2" t="inlineStr"/>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIUL TEHNIC ION MINCU</t>
+        </is>
+      </c>
       <c r="E159" t="n">
         <v>24</v>
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" s="3" t="n">
-        <v>1431.74</v>
+        <v>6.35</v>
       </c>
       <c r="H159" s="3" t="n"/>
       <c r="I159" s="3" t="n"/>
@@ -29654,11 +29658,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>COLEGIUL TEHNIC ION MINCU</t>
-        </is>
-      </c>
+      <c r="C160" s="2" t="inlineStr"/>
       <c r="E160" t="n">
         <v>24</v>
       </c>
@@ -29692,7 +29692,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="C162" s="2" t="inlineStr"/>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
+        </is>
+      </c>
       <c r="E162" t="n">
         <v>24</v>
       </c>
@@ -29709,11 +29713,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
-        </is>
-      </c>
+      <c r="C163" s="2" t="inlineStr"/>
       <c r="E163" t="n">
         <v>24</v>
       </c>
@@ -29730,7 +29730,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="C164" s="2" t="inlineStr"/>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Dulap vertical cu usi glisante</t>
+        </is>
+      </c>
       <c r="E164" t="n">
         <v>24</v>
       </c>
@@ -29747,17 +29751,13 @@
       </c>
     </row>
     <row r="165">
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Dulap vertical cu usi glisante</t>
-        </is>
-      </c>
+      <c r="C165" s="2" t="inlineStr"/>
       <c r="E165" t="n">
         <v>24</v>
       </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" s="3" t="n">
-        <v>6.35</v>
+        <v>161.39</v>
       </c>
       <c r="H165" s="3" t="n"/>
       <c r="I165" s="3" t="n"/>
@@ -29768,7 +29768,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="C166" s="2" t="inlineStr"/>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIUL NATIONAL AL.I.CUZA</t>
+        </is>
+      </c>
       <c r="E166" t="n">
         <v>24</v>
       </c>
@@ -29787,7 +29791,7 @@
     <row r="167">
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>COLEGIUL NATIONAL AL.I.CUZA</t>
+          <t>Demolare corp C2, construire si relocare punct termic</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -29806,11 +29810,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Demolare corp C2, construire si relocare punct termic</t>
-        </is>
-      </c>
+      <c r="C168" s="2" t="inlineStr"/>
       <c r="E168" t="n">
         <v>24</v>
       </c>
@@ -29833,7 +29833,7 @@
       </c>
       <c r="F169" t="inlineStr"/>
       <c r="G169" s="3" t="n">
-        <v>161.39</v>
+        <v>13</v>
       </c>
       <c r="H169" s="3" t="n"/>
       <c r="I169" s="3" t="n"/>
@@ -29844,7 +29844,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="C170" s="2" t="inlineStr"/>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>LICEUL DE ARTA GH.TATTARESCU</t>
+        </is>
+      </c>
       <c r="E170" t="n">
         <v>24</v>
       </c>
@@ -29863,7 +29867,7 @@
     <row r="171">
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>LICEUL DE ARTA GH.TATTARESCU</t>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -29882,11 +29886,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
-        </is>
-      </c>
+      <c r="C172" s="2" t="inlineStr"/>
       <c r="E172" t="n">
         <v>24</v>
       </c>
@@ -29903,7 +29903,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="C173" s="2" t="inlineStr"/>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Pompa de apa sediu str. Domei (2 buc)</t>
+        </is>
+      </c>
       <c r="E173" t="n">
         <v>24</v>
       </c>
@@ -29920,11 +29924,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>Pompa de apa sediu str. Domei (2 buc)</t>
-        </is>
-      </c>
+      <c r="C174" s="2" t="inlineStr"/>
       <c r="E174" t="n">
         <v>24</v>
       </c>
@@ -29941,13 +29941,17 @@
       </c>
     </row>
     <row r="175">
-      <c r="C175" s="2" t="inlineStr"/>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>SCOALA GIMNAZIALA DUILIU ZAMFIRESCU</t>
+        </is>
+      </c>
       <c r="E175" t="n">
         <v>24</v>
       </c>
       <c r="F175" t="inlineStr"/>
       <c r="G175" s="3" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="H175" s="3" t="n"/>
       <c r="I175" s="3" t="n"/>
@@ -29958,11 +29962,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>SCOALA GIMNAZIALA DUILIU ZAMFIRESCU</t>
-        </is>
-      </c>
+      <c r="C176" s="2" t="inlineStr"/>
       <c r="E176" t="n">
         <v>24</v>
       </c>
@@ -29996,7 +29996,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="C178" s="2" t="inlineStr"/>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
+        </is>
+      </c>
       <c r="E178" t="n">
         <v>24</v>
       </c>
@@ -30015,7 +30019,7 @@
     <row r="179">
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
+          <t>Masina de spalat vase profesionala</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -30023,7 +30027,7 @@
       </c>
       <c r="F179" t="inlineStr"/>
       <c r="G179" s="3" t="n">
-        <v>41</v>
+        <v>26.7</v>
       </c>
       <c r="H179" s="3" t="n"/>
       <c r="I179" s="3" t="n"/>
@@ -30034,11 +30038,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>Masina de spalat vase profesionala</t>
-        </is>
-      </c>
+      <c r="C180" s="2" t="inlineStr"/>
       <c r="E180" t="n">
         <v>24</v>
       </c>
@@ -30055,16 +30055,22 @@
       </c>
     </row>
     <row r="181">
-      <c r="C181" s="2" t="inlineStr"/>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Masina profesionala de curatat cartofi</t>
+        </is>
+      </c>
       <c r="E181" t="n">
         <v>24</v>
       </c>
       <c r="F181" t="inlineStr"/>
       <c r="G181" s="3" t="n">
-        <v>26.7</v>
+        <v>14.3</v>
       </c>
       <c r="H181" s="3" t="n"/>
-      <c r="I181" s="3" t="n"/>
+      <c r="I181" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J181" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30072,11 +30078,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>Masina profesionala de curatat cartofi</t>
-        </is>
-      </c>
+      <c r="C182" s="2" t="inlineStr"/>
       <c r="E182" t="n">
         <v>24</v>
       </c>
@@ -30085,9 +30087,7 @@
         <v>14.3</v>
       </c>
       <c r="H182" s="3" t="n"/>
-      <c r="I182" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I182" s="3" t="n"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30101,10 +30101,12 @@
       </c>
       <c r="F183" t="inlineStr"/>
       <c r="G183" s="3" t="n">
-        <v>14.3</v>
+        <v>980</v>
       </c>
       <c r="H183" s="3" t="n"/>
-      <c r="I183" s="3" t="n"/>
+      <c r="I183" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J183" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30121,9 +30123,7 @@
         <v>980</v>
       </c>
       <c r="H184" s="3" t="n"/>
-      <c r="I184" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I184" s="3" t="n"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30131,7 +30131,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="C185" s="2" t="inlineStr"/>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
+        </is>
+      </c>
       <c r="E185" t="n">
         <v>24</v>
       </c>
@@ -30140,7 +30144,9 @@
         <v>980</v>
       </c>
       <c r="H185" s="3" t="n"/>
-      <c r="I185" s="3" t="n"/>
+      <c r="I185" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J185" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30148,11 +30154,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
-        </is>
-      </c>
+      <c r="C186" s="2" t="inlineStr"/>
       <c r="E186" t="n">
         <v>24</v>
       </c>
@@ -30161,9 +30163,7 @@
         <v>980</v>
       </c>
       <c r="H186" s="3" t="n"/>
-      <c r="I186" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I186" s="3" t="n"/>
       <c r="J186" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30171,16 +30171,22 @@
       </c>
     </row>
     <row r="187">
-      <c r="C187" s="2" t="inlineStr"/>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Actualizarea documentatiei tehnico economice pentru proiectul</t>
+        </is>
+      </c>
       <c r="E187" t="n">
         <v>24</v>
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" s="3" t="n">
-        <v>980</v>
+        <v>250</v>
       </c>
       <c r="H187" s="3" t="n"/>
-      <c r="I187" s="3" t="n"/>
+      <c r="I187" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J187" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30190,7 +30196,7 @@
     <row r="188">
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Actualizarea documentatiei tehnico economice pentru proiectul</t>
+          <t>"Extinderea si modernizarea Scolii Duiliu Zamfirescu"</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -30201,9 +30207,7 @@
         <v>250</v>
       </c>
       <c r="H188" s="3" t="n"/>
-      <c r="I188" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I188" s="3" t="n"/>
       <c r="J188" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30213,7 +30217,7 @@
     <row r="189">
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>"Extinderea si modernizarea Scolii Duiliu Zamfirescu"</t>
+          <t>Documentatie tehnico-economica pentru proiectul "Modernizare</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -30221,7 +30225,7 @@
       </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" s="3" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H189" s="3" t="n"/>
       <c r="I189" s="3" t="n"/>
@@ -30234,7 +30238,7 @@
     <row r="190">
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica pentru proiectul "Modernizare</t>
+          <t>terenuri de sport din incinta unitatilor de invatamant</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -30255,7 +30259,7 @@
     <row r="191">
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>terenuri de sport din incinta unitatilor de invatamant</t>
+          <t>Documentatie tehnico-economica pentru proiectul "Cladire</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -30263,7 +30267,7 @@
       </c>
       <c r="F191" t="inlineStr"/>
       <c r="G191" s="3" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="H191" s="3" t="n"/>
       <c r="I191" s="3" t="n"/>
@@ -30276,7 +30280,7 @@
     <row r="192">
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica pentru proiectul "Cladire</t>
+          <t>administrativa pentru activitati scolare la Liceul de Arta Gh.Tattarascu" Documentatie tehnico-economica pentru Reabilitarea si</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -30297,7 +30301,7 @@
     <row r="193">
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>administrativa pentru activitati scolare la Liceul de Arta Gh.Tattarascu" Documentatie tehnico-economica pentru Reabilitarea si</t>
+          <t>modernizare corp de cladire gradinita din str. Tineretii nr. 7</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -30305,7 +30309,7 @@
       </c>
       <c r="F193" t="inlineStr"/>
       <c r="G193" s="3" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="H193" s="3" t="n"/>
       <c r="I193" s="3" t="n"/>
@@ -30318,7 +30322,7 @@
     <row r="194">
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>modernizare corp de cladire gradinita din str. Tineretii nr. 7</t>
+          <t>Focsani</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -30339,7 +30343,7 @@
     <row r="195">
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Focsani</t>
+          <t>Documentatie tehnico-economica -Instalare surse secundare de producere agent termic local la corpurile de scoala principale ale unitatilor de invatamant alimentate din sistemul public de</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -30347,7 +30351,7 @@
       </c>
       <c r="F195" t="inlineStr"/>
       <c r="G195" s="3" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H195" s="3" t="n"/>
       <c r="I195" s="3" t="n"/>
@@ -30360,7 +30364,7 @@
     <row r="196">
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica -Instalare surse secundare de producere agent termic local la corpurile de scoala principale ale unitatilor de invatamant alimentate din sistemul public de</t>
+          <t>termoficare (20 unitati de invatamant)</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -30379,17 +30383,13 @@
       </c>
     </row>
     <row r="197">
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>termoficare (20 unitati de invatamant)</t>
-        </is>
-      </c>
+      <c r="C197" s="2" t="inlineStr"/>
       <c r="E197" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F197" t="inlineStr"/>
       <c r="G197" s="3" t="n">
-        <v>250</v>
+        <v>164</v>
       </c>
       <c r="H197" s="3" t="n"/>
       <c r="I197" s="3" t="n"/>
@@ -30400,7 +30400,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="C198" s="2" t="inlineStr"/>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIUL NATIONAL UNIREA</t>
+        </is>
+      </c>
       <c r="E198" t="n">
         <v>25</v>
       </c>
@@ -30419,7 +30423,7 @@
     <row r="199">
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>COLEGIUL NATIONAL UNIREA</t>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -30430,7 +30434,9 @@
         <v>164</v>
       </c>
       <c r="H199" s="3" t="n"/>
-      <c r="I199" s="3" t="n"/>
+      <c r="I199" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J199" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30438,11 +30444,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
-        </is>
-      </c>
+      <c r="C200" s="2" t="inlineStr"/>
       <c r="E200" t="n">
         <v>25</v>
       </c>
@@ -30451,9 +30453,7 @@
         <v>164</v>
       </c>
       <c r="H200" s="3" t="n"/>
-      <c r="I200" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I200" s="3" t="n"/>
       <c r="J200" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30461,13 +30461,17 @@
       </c>
     </row>
     <row r="201">
-      <c r="C201" s="2" t="inlineStr"/>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>Documentatie tehnico-economica demolare cladire si relocare</t>
+        </is>
+      </c>
       <c r="E201" t="n">
         <v>25</v>
       </c>
       <c r="F201" t="inlineStr"/>
       <c r="G201" s="3" t="n">
-        <v>164</v>
+        <v>32</v>
       </c>
       <c r="H201" s="3" t="n"/>
       <c r="I201" s="3" t="n"/>
@@ -30480,7 +30484,7 @@
     <row r="202">
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica demolare cladire si relocare</t>
+          <t>centrala termica</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -30499,17 +30503,13 @@
       </c>
     </row>
     <row r="203">
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>centrala termica</t>
-        </is>
-      </c>
+      <c r="C203" s="2" t="inlineStr"/>
       <c r="E203" t="n">
         <v>25</v>
       </c>
       <c r="F203" t="inlineStr"/>
       <c r="G203" s="3" t="n">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="H203" s="3" t="n"/>
       <c r="I203" s="3" t="n"/>
@@ -30520,7 +30520,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="C204" s="2" t="inlineStr"/>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Centrala termica (inclusiv montaj)</t>
+        </is>
+      </c>
       <c r="E204" t="n">
         <v>25</v>
       </c>
@@ -30537,20 +30541,18 @@
       </c>
     </row>
     <row r="205">
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>Centrala termica (inclusiv montaj)</t>
-        </is>
-      </c>
+      <c r="C205" s="2" t="inlineStr"/>
       <c r="E205" t="n">
         <v>25</v>
       </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" s="3" t="n">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="H205" s="3" t="n"/>
-      <c r="I205" s="3" t="n"/>
+      <c r="I205" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J205" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30558,7 +30560,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="C206" s="2" t="inlineStr"/>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIUL TEHNIC AUTO TRAIAN VUIA</t>
+        </is>
+      </c>
       <c r="E206" t="n">
         <v>25</v>
       </c>
@@ -30567,9 +30573,7 @@
         <v>66</v>
       </c>
       <c r="H206" s="3" t="n"/>
-      <c r="I206" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I206" s="3" t="n"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30579,7 +30583,7 @@
     <row r="207">
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>COLEGIUL TEHNIC AUTO TRAIAN VUIA</t>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -30598,11 +30602,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
-        </is>
-      </c>
+      <c r="C208" s="2" t="inlineStr"/>
       <c r="E208" t="n">
         <v>25</v>
       </c>
@@ -30619,7 +30619,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="C209" s="2" t="inlineStr"/>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>Documentatie tehnico-economica conservare lucrari la stadiul fizic existent pentru obiectivul "Construire sala de sport +ateliere si</t>
+        </is>
+      </c>
       <c r="E209" t="n">
         <v>25</v>
       </c>
@@ -30638,7 +30642,7 @@
     <row r="210">
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica conservare lucrari la stadiul fizic existent pentru obiectivul "Construire sala de sport +ateliere si</t>
+          <t>anexe , D+P+E"</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -30657,19 +30661,17 @@
       </c>
     </row>
     <row r="211">
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>anexe , D+P+E"</t>
-        </is>
-      </c>
+      <c r="C211" s="2" t="inlineStr"/>
       <c r="E211" t="n">
         <v>25</v>
       </c>
       <c r="F211" t="inlineStr"/>
       <c r="G211" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="H211" s="3" t="n"/>
+        <v>462</v>
+      </c>
+      <c r="H211" s="3" t="n">
+        <v>66.02</v>
+      </c>
       <c r="I211" s="3" t="n"/>
       <c r="J211" t="inlineStr">
         <is>
@@ -30678,7 +30680,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="C212" s="2" t="inlineStr"/>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>SANATATE</t>
+        </is>
+      </c>
       <c r="E212" t="n">
         <v>25</v>
       </c>
@@ -30686,9 +30692,7 @@
       <c r="G212" s="3" t="n">
         <v>462</v>
       </c>
-      <c r="H212" s="3" t="n">
-        <v>66.02</v>
-      </c>
+      <c r="H212" s="3" t="n"/>
       <c r="I212" s="3" t="n"/>
       <c r="J212" t="inlineStr">
         <is>
@@ -30697,11 +30701,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>SANATATE</t>
-        </is>
-      </c>
+      <c r="C213" s="2" t="inlineStr"/>
       <c r="E213" t="n">
         <v>25</v>
       </c>
@@ -30718,7 +30718,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="C214" s="2" t="inlineStr"/>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>DIRECTIA DE ASISTENTA SOCIALA</t>
+        </is>
+      </c>
       <c r="E214" t="n">
         <v>25</v>
       </c>
@@ -30737,7 +30741,7 @@
     <row r="215">
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>DIRECTIA DE ASISTENTA SOCIALA</t>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -30756,11 +30760,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
-        </is>
-      </c>
+      <c r="C216" s="2" t="inlineStr"/>
       <c r="E216" t="n">
         <v>25</v>
       </c>
@@ -30783,10 +30783,12 @@
       </c>
       <c r="F217" t="inlineStr"/>
       <c r="G217" s="3" t="n">
-        <v>462</v>
+        <v>30</v>
       </c>
       <c r="H217" s="3" t="n"/>
-      <c r="I217" s="3" t="n"/>
+      <c r="I217" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J217" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30794,7 +30796,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="C218" s="2" t="inlineStr"/>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>Centrala termica Dispensar Sud</t>
+        </is>
+      </c>
       <c r="E218" t="n">
         <v>25</v>
       </c>
@@ -30803,9 +30809,7 @@
         <v>30</v>
       </c>
       <c r="H218" s="3" t="n"/>
-      <c r="I218" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I218" s="3" t="n"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30815,7 +30819,7 @@
     <row r="219">
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Centrala termica Dispensar Sud</t>
+          <t>Platforma hidraulica transport persoane Dispensar Sud</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -30823,10 +30827,12 @@
       </c>
       <c r="F219" t="inlineStr"/>
       <c r="G219" s="3" t="n">
-        <v>30</v>
+        <v>152</v>
       </c>
       <c r="H219" s="3" t="n"/>
-      <c r="I219" s="3" t="n"/>
+      <c r="I219" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J219" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30834,11 +30840,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>Platforma hidraulica transport persoane Dispensar Sud</t>
-        </is>
-      </c>
+      <c r="C220" s="2" t="inlineStr"/>
       <c r="E220" t="n">
         <v>25</v>
       </c>
@@ -30847,9 +30849,7 @@
         <v>152</v>
       </c>
       <c r="H220" s="3" t="n"/>
-      <c r="I220" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I220" s="3" t="n"/>
       <c r="J220" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30857,13 +30857,17 @@
       </c>
     </row>
     <row r="221">
-      <c r="C221" s="2" t="inlineStr"/>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>Unit dentar (5 buc)</t>
+        </is>
+      </c>
       <c r="E221" t="n">
         <v>25</v>
       </c>
       <c r="F221" t="inlineStr"/>
       <c r="G221" s="3" t="n">
-        <v>152</v>
+        <v>280</v>
       </c>
       <c r="H221" s="3" t="n"/>
       <c r="I221" s="3" t="n"/>
@@ -30874,11 +30878,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>Unit dentar (5 buc)</t>
-        </is>
-      </c>
+      <c r="C222" s="2" t="inlineStr"/>
       <c r="E222" t="n">
         <v>25</v>
       </c>
@@ -30895,15 +30895,21 @@
       </c>
     </row>
     <row r="223">
-      <c r="C223" s="2" t="inlineStr"/>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>CULTURÃ, RECREERE ŞI RELIGIE</t>
+        </is>
+      </c>
       <c r="E223" t="n">
         <v>25</v>
       </c>
       <c r="F223" t="inlineStr"/>
       <c r="G223" s="3" t="n">
-        <v>280</v>
-      </c>
-      <c r="H223" s="3" t="n"/>
+        <v>785</v>
+      </c>
+      <c r="H223" s="3" t="n">
+        <v>67.02</v>
+      </c>
       <c r="I223" s="3" t="n"/>
       <c r="J223" t="inlineStr">
         <is>
@@ -30912,11 +30918,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>CULTURÃ, RECREERE ŞI RELIGIE</t>
-        </is>
-      </c>
+      <c r="C224" s="2" t="inlineStr"/>
       <c r="E224" t="n">
         <v>25</v>
       </c>
@@ -30924,10 +30926,10 @@
       <c r="G224" s="3" t="n">
         <v>785</v>
       </c>
-      <c r="H224" s="3" t="n">
-        <v>67.02</v>
-      </c>
-      <c r="I224" s="3" t="n"/>
+      <c r="H224" s="3" t="n"/>
+      <c r="I224" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J224" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30935,7 +30937,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="C225" s="2" t="inlineStr"/>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI ALTE CHELTUIELI DE INVESTITII</t>
+        </is>
+      </c>
       <c r="E225" t="n">
         <v>25</v>
       </c>
@@ -30944,9 +30950,7 @@
         <v>785</v>
       </c>
       <c r="H225" s="3" t="n"/>
-      <c r="I225" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I225" s="3" t="n"/>
       <c r="J225" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -30954,17 +30958,13 @@
       </c>
     </row>
     <row r="226">
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI ALTE CHELTUIELI DE INVESTITII</t>
-        </is>
-      </c>
+      <c r="C226" s="2" t="inlineStr"/>
       <c r="E226" t="n">
         <v>25</v>
       </c>
       <c r="F226" t="inlineStr"/>
       <c r="G226" s="3" t="n">
-        <v>785</v>
+        <v>200</v>
       </c>
       <c r="H226" s="3" t="n"/>
       <c r="I226" s="3" t="n"/>
@@ -30975,7 +30975,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="C227" s="2" t="inlineStr"/>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>Documentatie tehnico-economica pentru proiectul "Construire Centru Multifunctional pentru copii si tineret"</t>
+        </is>
+      </c>
       <c r="E227" t="n">
         <v>25</v>
       </c>
@@ -30994,7 +30998,7 @@
     <row r="228">
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica pentru proiectul "Construire Centru Multifunctional pentru copii si tineret"</t>
+          <t>Documentatie tehnico-economica Reabilitare si regenerare</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -31005,7 +31009,9 @@
         <v>200</v>
       </c>
       <c r="H228" s="3" t="n"/>
-      <c r="I228" s="3" t="n"/>
+      <c r="I228" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J228" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -31015,7 +31021,7 @@
     <row r="229">
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica Reabilitare si regenerare</t>
+          <t>zona parc Teatru</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -31026,9 +31032,7 @@
         <v>200</v>
       </c>
       <c r="H229" s="3" t="n"/>
-      <c r="I229" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I229" s="3" t="n"/>
       <c r="J229" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -31038,7 +31042,7 @@
     <row r="230">
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>zona parc Teatru</t>
+          <t>Documentatie tehnico-economica pentru infiintarea unei</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -31046,7 +31050,7 @@
       </c>
       <c r="F230" t="inlineStr"/>
       <c r="G230" s="3" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="H230" s="3" t="n"/>
       <c r="I230" s="3" t="n"/>
@@ -31059,7 +31063,7 @@
     <row r="231">
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica pentru infiintarea unei</t>
+          <t>paduri in Mandresti</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -31080,7 +31084,7 @@
     <row r="232">
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>paduri in Mandresti</t>
+          <t>Documentatie tehnico-economica Reabilitare si</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -31088,7 +31092,7 @@
       </c>
       <c r="F232" t="inlineStr"/>
       <c r="G232" s="3" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H232" s="3" t="n"/>
       <c r="I232" s="3" t="n"/>
@@ -31101,7 +31105,7 @@
     <row r="233">
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica Reabilitare si</t>
+          <t>modernizarea insfrastructurii verzi din Parcul Schumman</t>
         </is>
       </c>
       <c r="E233" t="n">
@@ -31122,7 +31126,7 @@
     <row r="234">
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>modernizarea insfrastructurii verzi din Parcul Schumman</t>
+          <t>Documentatie tehnico-economica spatii de agrement si</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -31133,7 +31137,9 @@
         <v>130</v>
       </c>
       <c r="H234" s="3" t="n"/>
-      <c r="I234" s="3" t="n"/>
+      <c r="I234" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J234" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -31143,7 +31149,7 @@
     <row r="235">
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica spatii de agrement si</t>
+          <t>joaca in Mun.Focsani ASIGURĂRI ŞI ASISTENTĂ SOCIALĂ DIRECTIA DE ASISTENTA SOCIALA ALTE CHELTUIELI DE INVESTITII</t>
         </is>
       </c>
       <c r="E235" t="n">
@@ -31153,10 +31159,10 @@
       <c r="G235" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="H235" s="3" t="n"/>
-      <c r="I235" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="H235" s="3" t="n">
+        <v>68.02</v>
+      </c>
+      <c r="I235" s="3" t="n"/>
       <c r="J235" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -31166,19 +31172,15 @@
     <row r="236">
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>joaca in Mun.Focsani ASIGURĂRI ŞI ASISTENTĂ SOCIALĂ DIRECTIA DE ASISTENTA SOCIALA ALTE CHELTUIELI DE INVESTITII</t>
+          <t>CAPITOL/OBIECTIV</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F236" t="inlineStr"/>
-      <c r="G236" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="H236" s="3" t="n">
-        <v>68.02</v>
-      </c>
+      <c r="G236" s="3" t="n"/>
+      <c r="H236" s="3" t="n"/>
       <c r="I236" s="3" t="n"/>
       <c r="J236" t="inlineStr">
         <is>
@@ -31189,14 +31191,16 @@
     <row r="237">
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>CAPITOL/OBIECTIV</t>
+          <t>Documentatie tehnico-economica privind implementarea</t>
         </is>
       </c>
       <c r="E237" t="n">
         <v>26</v>
       </c>
       <c r="F237" t="inlineStr"/>
-      <c r="G237" s="3" t="n"/>
+      <c r="G237" s="3" t="n">
+        <v>200</v>
+      </c>
       <c r="H237" s="3" t="n"/>
       <c r="I237" s="3" t="n"/>
       <c r="J237" t="inlineStr">
@@ -31208,7 +31212,7 @@
     <row r="238">
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica privind implementarea</t>
+          <t>unui sistem de incalzire propriu la Caminul de Batrani</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -31229,17 +31233,17 @@
     <row r="239">
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>unui sistem de incalzire propriu la Caminul de Batrani</t>
+          <t>LOCUINTE, SERVICII ŞI DEZVOLTARE PUBLICÃ</t>
         </is>
       </c>
       <c r="E239" t="n">
         <v>26</v>
       </c>
       <c r="F239" t="inlineStr"/>
-      <c r="G239" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="H239" s="3" t="n"/>
+      <c r="G239" s="3" t="n"/>
+      <c r="H239" s="3" t="n">
+        <v>70.02</v>
+      </c>
       <c r="I239" s="3" t="n"/>
       <c r="J239" t="inlineStr">
         <is>
@@ -31250,17 +31254,17 @@
     <row r="240">
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>LOCUINTE, SERVICII ŞI DEZVOLTARE PUBLICÃ</t>
+          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI Modernizarea sistemului de iluminat public din</t>
         </is>
       </c>
       <c r="E240" t="n">
         <v>26</v>
       </c>
       <c r="F240" t="inlineStr"/>
-      <c r="G240" s="3" t="n"/>
-      <c r="H240" s="3" t="n">
-        <v>70.02</v>
-      </c>
+      <c r="G240" s="3" t="n">
+        <v>21604.73</v>
+      </c>
+      <c r="H240" s="3" t="n"/>
       <c r="I240" s="3" t="n"/>
       <c r="J240" t="inlineStr">
         <is>
@@ -31271,7 +31275,7 @@
     <row r="241">
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI Modernizarea sistemului de iluminat public din</t>
+          <t>Mun.Focsani (AFM) etapa II</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -31279,7 +31283,7 @@
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" s="3" t="n">
-        <v>21604.73</v>
+        <v>6203.96</v>
       </c>
       <c r="H241" s="3" t="n"/>
       <c r="I241" s="3" t="n"/>
@@ -31292,7 +31296,7 @@
     <row r="242">
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Mun.Focsani (AFM) etapa II</t>
+          <t>Modernizarea sistemului de iluminat public din Mun.Focsani (AFM) etapa III</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -31300,7 +31304,7 @@
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" s="3" t="n">
-        <v>6203.96</v>
+        <v>6688.33</v>
       </c>
       <c r="H242" s="3" t="n"/>
       <c r="I242" s="3" t="n"/>
@@ -31311,11 +31315,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>Modernizarea sistemului de iluminat public din Mun.Focsani (AFM) etapa III</t>
-        </is>
-      </c>
+      <c r="C243" s="2" t="inlineStr"/>
       <c r="E243" t="n">
         <v>26</v>
       </c>
@@ -31332,13 +31332,17 @@
       </c>
     </row>
     <row r="244">
-      <c r="C244" s="2" t="inlineStr"/>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>Sistematizare verticala si modernizare retele utilitati publice</t>
+        </is>
+      </c>
       <c r="E244" t="n">
         <v>26</v>
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" s="3" t="n">
-        <v>6688.33</v>
+        <v>3451.08</v>
       </c>
       <c r="H244" s="3" t="n"/>
       <c r="I244" s="3" t="n"/>
@@ -31351,7 +31355,7 @@
     <row r="245">
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Sistematizare verticala si modernizare retele utilitati publice</t>
+          <t>in ansamblu rezidential din str.Comisia Centrala. Construire spatii depozitare str.Cuza-Voda nr. 56</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -31362,7 +31366,9 @@
         <v>3451.08</v>
       </c>
       <c r="H245" s="3" t="n"/>
-      <c r="I245" s="3" t="n"/>
+      <c r="I245" s="3" t="n">
+        <v>194.85</v>
+      </c>
       <c r="J245" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -31372,7 +31378,7 @@
     <row r="246">
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>in ansamblu rezidential din str.Comisia Centrala. Construire spatii depozitare str.Cuza-Voda nr. 56</t>
+          <t>Retea interioara distributie energie electrica Bloc C2</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -31380,12 +31386,10 @@
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" s="3" t="n">
-        <v>3451.08</v>
+        <v>213.2</v>
       </c>
       <c r="H246" s="3" t="n"/>
-      <c r="I246" s="3" t="n">
-        <v>194.85</v>
-      </c>
+      <c r="I246" s="3" t="n"/>
       <c r="J246" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -31395,7 +31399,7 @@
     <row r="247">
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Retea interioara distributie energie electrica Bloc C2</t>
+          <t>Tronson 1 din str. Revolutie nr.16</t>
         </is>
       </c>
       <c r="E247" t="n">
@@ -31416,7 +31420,7 @@
     <row r="248">
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Tronson 1 din str. Revolutie nr.16</t>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -31424,7 +31428,7 @@
       </c>
       <c r="F248" t="inlineStr"/>
       <c r="G248" s="3" t="n">
-        <v>213.2</v>
+        <v>4853.31</v>
       </c>
       <c r="H248" s="3" t="n"/>
       <c r="I248" s="3" t="n"/>
@@ -31437,7 +31441,7 @@
     <row r="249">
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
+          <t>_Studii topo și geo</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -31458,7 +31462,7 @@
     <row r="250">
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>_Studii topo și geo</t>
+          <t>_Expertize tehnice si verificari proiecte _PUZ strapungere DN23-Drum acces Statia de Epurare</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -31466,10 +31470,12 @@
       </c>
       <c r="F250" t="inlineStr"/>
       <c r="G250" s="3" t="n">
-        <v>4853.31</v>
+        <v>20</v>
       </c>
       <c r="H250" s="3" t="n"/>
-      <c r="I250" s="3" t="n"/>
+      <c r="I250" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J250" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -31477,22 +31483,16 @@
       </c>
     </row>
     <row r="251">
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>_Expertize tehnice si verificari proiecte _PUZ strapungere DN23-Drum acces Statia de Epurare</t>
-        </is>
-      </c>
+      <c r="C251" s="2" t="inlineStr"/>
       <c r="E251" t="n">
         <v>26</v>
       </c>
       <c r="F251" t="inlineStr"/>
       <c r="G251" s="3" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="H251" s="3" t="n"/>
-      <c r="I251" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I251" s="3" t="n"/>
       <c r="J251" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -31500,13 +31500,17 @@
       </c>
     </row>
     <row r="252">
-      <c r="C252" s="2" t="inlineStr"/>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Taxe diverse si tarife obtinere avize, acorduri, autorizatii pentru documentatii si obiective de investitii</t>
+        </is>
+      </c>
       <c r="E252" t="n">
         <v>26</v>
       </c>
       <c r="F252" t="inlineStr"/>
       <c r="G252" s="3" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H252" s="3" t="n"/>
       <c r="I252" s="3" t="n"/>
@@ -31519,7 +31523,7 @@
     <row r="253">
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Taxe diverse si tarife obtinere avize, acorduri, autorizatii pentru documentatii si obiective de investitii</t>
+          <t>Documentatie-PUZ -Zona construita protejata (Studii preliminare, studii de specialitate, elaborare PUZ CP si RLU)</t>
         </is>
       </c>
       <c r="E253" t="n">
@@ -31540,7 +31544,7 @@
     <row r="254">
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Documentatie-PUZ -Zona construita protejata (Studii preliminare, studii de specialitate, elaborare PUZ CP si RLU)</t>
+          <t>Documentatie Alimentare cu energie Statii de pompare ape</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -31548,7 +31552,7 @@
       </c>
       <c r="F254" t="inlineStr"/>
       <c r="G254" s="3" t="n">
-        <v>30</v>
+        <v>706.24</v>
       </c>
       <c r="H254" s="3" t="n"/>
       <c r="I254" s="3" t="n"/>
@@ -31561,7 +31565,7 @@
     <row r="255">
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Documentatie Alimentare cu energie Statii de pompare ape</t>
+          <t>uzate Documentatie tehnico-economica ,,Sistematizare verticala si modernizare retele utilitati publice in ansamblu rezidential din str.Comisia Centrala.</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -31582,7 +31586,7 @@
     <row r="256">
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>uzate Documentatie tehnico-economica ,,Sistematizare verticala si modernizare retele utilitati publice in ansamblu rezidential din str.Comisia Centrala.</t>
+          <t>Documentatie-tehnico economica PUZ -Zona lotizata - Sprijin acordat tinerilor pentru construirea unor locuinte proprietate personala conf L 15/2023 Cazan incalzire blocuri ANL (2 buc) Documentatii evaluare vizuala rapida a constructiilor</t>
         </is>
       </c>
       <c r="E256" t="n">
@@ -31590,7 +31594,7 @@
       </c>
       <c r="F256" t="inlineStr"/>
       <c r="G256" s="3" t="n">
-        <v>706.24</v>
+        <v>320</v>
       </c>
       <c r="H256" s="3" t="n"/>
       <c r="I256" s="3" t="n"/>
@@ -31603,7 +31607,7 @@
     <row r="257">
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Documentatie-tehnico economica PUZ -Zona lotizata - Sprijin acordat tinerilor pentru construirea unor locuinte proprietate personala conf L 15/2023 Cazan incalzire blocuri ANL (2 buc) Documentatii evaluare vizuala rapida a constructiilor</t>
+          <t>conform Legii 212/2022</t>
         </is>
       </c>
       <c r="E257" t="n">
@@ -31611,7 +31615,7 @@
       </c>
       <c r="F257" t="inlineStr"/>
       <c r="G257" s="3" t="n">
-        <v>320</v>
+        <v>208.25</v>
       </c>
       <c r="H257" s="3" t="n"/>
       <c r="I257" s="3" t="n"/>
@@ -31624,7 +31628,7 @@
     <row r="258">
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>conform Legii 212/2022</t>
+          <t>Documentatie tehnico-economica pentru proiectul "Regenerare urbana a zonei centrale a Municipiului</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -31632,10 +31636,12 @@
       </c>
       <c r="F258" t="inlineStr"/>
       <c r="G258" s="3" t="n">
-        <v>208.25</v>
+        <v>250</v>
       </c>
       <c r="H258" s="3" t="n"/>
-      <c r="I258" s="3" t="n"/>
+      <c r="I258" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J258" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -31645,7 +31651,7 @@
     <row r="259">
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica pentru proiectul "Regenerare urbana a zonei centrale a Municipiului</t>
+          <t>Focsani"</t>
         </is>
       </c>
       <c r="E259" t="n">
@@ -31656,9 +31662,7 @@
         <v>250</v>
       </c>
       <c r="H259" s="3" t="n"/>
-      <c r="I259" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I259" s="3" t="n"/>
       <c r="J259" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -31668,7 +31672,7 @@
     <row r="260">
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Focsani"</t>
+          <t>Actualizare Strategie Integrata de Dezvoltare Urbana 2021-</t>
         </is>
       </c>
       <c r="E260" t="n">
@@ -31676,7 +31680,7 @@
       </c>
       <c r="F260" t="inlineStr"/>
       <c r="G260" s="3" t="n">
-        <v>250</v>
+        <v>196.35</v>
       </c>
       <c r="H260" s="3" t="n"/>
       <c r="I260" s="3" t="n"/>
@@ -31689,7 +31693,7 @@
     <row r="261">
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Actualizare Strategie Integrata de Dezvoltare Urbana 2021-</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="E261" t="n">
@@ -31710,7 +31714,7 @@
     <row r="262">
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>Documentatie-tehnico economica Retele de alimentare cu apa si canalizare in zona lotizata -Sprijin acordat tinerilor</t>
         </is>
       </c>
       <c r="E262" t="n">
@@ -31718,7 +31722,7 @@
       </c>
       <c r="F262" t="inlineStr"/>
       <c r="G262" s="3" t="n">
-        <v>196.35</v>
+        <v>70</v>
       </c>
       <c r="H262" s="3" t="n"/>
       <c r="I262" s="3" t="n"/>
@@ -31731,7 +31735,7 @@
     <row r="263">
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Documentatie-tehnico economica Retele de alimentare cu apa si canalizare in zona lotizata -Sprijin acordat tinerilor</t>
+          <t>pentru construirea unor locuinte proprietate personala conf L15/2023</t>
         </is>
       </c>
       <c r="E263" t="n">
@@ -31750,17 +31754,13 @@
       </c>
     </row>
     <row r="264">
-      <c r="C264" s="2" t="inlineStr">
-        <is>
-          <t>pentru construirea unor locuinte proprietate personala conf L15/2023</t>
-        </is>
-      </c>
+      <c r="C264" s="2" t="inlineStr"/>
       <c r="E264" t="n">
         <v>26</v>
       </c>
       <c r="F264" t="inlineStr"/>
       <c r="G264" s="3" t="n">
-        <v>70</v>
+        <v>95.08</v>
       </c>
       <c r="H264" s="3" t="n"/>
       <c r="I264" s="3" t="n"/>
@@ -31771,7 +31771,11 @@
       </c>
     </row>
     <row r="265">
-      <c r="C265" s="2" t="inlineStr"/>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>_Documentatie tehnico-economica pentru Cresterea performantei energetice a cladirii Directiei de Asistenta Sociala si a Politiei Locale</t>
+        </is>
+      </c>
       <c r="E265" t="n">
         <v>26</v>
       </c>
@@ -31790,7 +31794,7 @@
     <row r="266">
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>_Documentatie tehnico-economica pentru Cresterea performantei energetice a cladirii Directiei de Asistenta Sociala si a Politiei Locale</t>
+          <t>_Documentatie tehnico-economica pentru Cresterea performantei energetice a cladirii Parking</t>
         </is>
       </c>
       <c r="E266" t="n">
@@ -31809,11 +31813,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="C267" s="2" t="inlineStr">
-        <is>
-          <t>_Documentatie tehnico-economica pentru Cresterea performantei energetice a cladirii Parking</t>
-        </is>
-      </c>
+      <c r="C267" s="2" t="inlineStr"/>
       <c r="E267" t="n">
         <v>26</v>
       </c>
@@ -31830,14 +31830,16 @@
       </c>
     </row>
     <row r="268">
-      <c r="C268" s="2" t="inlineStr"/>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>CAPITOL/OBIECTIV</t>
+        </is>
+      </c>
       <c r="E268" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F268" t="inlineStr"/>
-      <c r="G268" s="3" t="n">
-        <v>95.08</v>
-      </c>
+      <c r="G268" s="3" t="n"/>
       <c r="H268" s="3" t="n"/>
       <c r="I268" s="3" t="n"/>
       <c r="J268" t="inlineStr">
@@ -31849,14 +31851,16 @@
     <row r="269">
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>CAPITOL/OBIECTIV</t>
+          <t>_Documentatie tehnico-economica pentru Reabilitare</t>
         </is>
       </c>
       <c r="E269" t="n">
         <v>27</v>
       </c>
       <c r="F269" t="inlineStr"/>
-      <c r="G269" s="3" t="n"/>
+      <c r="G269" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="H269" s="3" t="n"/>
       <c r="I269" s="3" t="n"/>
       <c r="J269" t="inlineStr">
@@ -31868,7 +31872,7 @@
     <row r="270">
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>_Documentatie tehnico-economica pentru Reabilitare</t>
+          <t>Gradina de Vara Municipiul Focsani</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -31889,7 +31893,7 @@
     <row r="271">
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Gradina de Vara Municipiul Focsani</t>
+          <t>_Documentatie tehnico-economica Faza SF pentru proiectul Capacitati de productie energie electrica din</t>
         </is>
       </c>
       <c r="E271" t="n">
@@ -31897,7 +31901,7 @@
       </c>
       <c r="F271" t="inlineStr"/>
       <c r="G271" s="3" t="n">
-        <v>100</v>
+        <v>655.63</v>
       </c>
       <c r="H271" s="3" t="n"/>
       <c r="I271" s="3" t="n"/>
@@ -31910,7 +31914,7 @@
     <row r="272">
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>_Documentatie tehnico-economica Faza SF pentru proiectul Capacitati de productie energie electrica din</t>
+          <t>surse regenerabile de energie pentru cosumul propriu al Municipiului Focsani</t>
         </is>
       </c>
       <c r="E272" t="n">
@@ -31931,7 +31935,7 @@
     <row r="273">
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>surse regenerabile de energie pentru cosumul propriu al Municipiului Focsani</t>
+          <t>Actualizare documentatie tennico-economica pentru proiectul Consolidarea , restaurarea si dotarea imobilului</t>
         </is>
       </c>
       <c r="E273" t="n">
@@ -31939,10 +31943,12 @@
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" s="3" t="n">
-        <v>655.63</v>
+        <v>281.18</v>
       </c>
       <c r="H273" s="3" t="n"/>
-      <c r="I273" s="3" t="n"/>
+      <c r="I273" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J273" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -31952,7 +31958,7 @@
     <row r="274">
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Actualizare documentatie tennico-economica pentru proiectul Consolidarea , restaurarea si dotarea imobilului</t>
+          <t>din Bd. Garii nr. 10, Casa Longinescu-Cod LMI VN-Il-m-B- 06434</t>
         </is>
       </c>
       <c r="E274" t="n">
@@ -31963,9 +31969,7 @@
         <v>281.18</v>
       </c>
       <c r="H274" s="3" t="n"/>
-      <c r="I274" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I274" s="3" t="n"/>
       <c r="J274" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -31975,7 +31979,7 @@
     <row r="275">
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>din Bd. Garii nr. 10, Casa Longinescu-Cod LMI VN-Il-m-B- 06434</t>
+          <t>Linia 46 General Construct Focsani</t>
         </is>
       </c>
       <c r="E275" t="n">
@@ -31983,7 +31987,7 @@
       </c>
       <c r="F275" t="inlineStr"/>
       <c r="G275" s="3" t="n">
-        <v>281.18</v>
+        <v>43.5</v>
       </c>
       <c r="H275" s="3" t="n"/>
       <c r="I275" s="3" t="n"/>
@@ -31994,11 +31998,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="C276" s="2" t="inlineStr">
-        <is>
-          <t>Linia 46 General Construct Focsani</t>
-        </is>
-      </c>
+      <c r="C276" s="2" t="inlineStr"/>
       <c r="E276" t="n">
         <v>27</v>
       </c>
@@ -32015,13 +32015,17 @@
       </c>
     </row>
     <row r="277">
-      <c r="C277" s="2" t="inlineStr"/>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>Documentatie tehnico-economica Sistematizare verticala si racordare la utilitati Locuinte pentru tineri destinate</t>
+        </is>
+      </c>
       <c r="E277" t="n">
         <v>27</v>
       </c>
       <c r="F277" t="inlineStr"/>
       <c r="G277" s="3" t="n">
-        <v>43.5</v>
+        <v>120</v>
       </c>
       <c r="H277" s="3" t="n"/>
       <c r="I277" s="3" t="n"/>
@@ -32034,7 +32038,7 @@
     <row r="278">
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica Sistematizare verticala si racordare la utilitati Locuinte pentru tineri destinate</t>
+          <t>inchirierii , Mun Focsani, calea Munteniei nr.57</t>
         </is>
       </c>
       <c r="E278" t="n">
@@ -32055,7 +32059,7 @@
     <row r="279">
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>inchirierii , Mun Focsani, calea Munteniei nr.57</t>
+          <t>DIRECTIA DE DEZVOLTARE SERVICII PUBLICE</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -32063,7 +32067,7 @@
       </c>
       <c r="F279" t="inlineStr"/>
       <c r="G279" s="3" t="n">
-        <v>120</v>
+        <v>320</v>
       </c>
       <c r="H279" s="3" t="n"/>
       <c r="I279" s="3" t="n"/>
@@ -32074,11 +32078,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="C280" s="2" t="inlineStr">
-        <is>
-          <t>DIRECTIA DE DEZVOLTARE SERVICII PUBLICE</t>
-        </is>
-      </c>
+      <c r="C280" s="2" t="inlineStr"/>
       <c r="E280" t="n">
         <v>27</v>
       </c>
@@ -32095,7 +32095,11 @@
       </c>
     </row>
     <row r="281">
-      <c r="C281" s="2" t="inlineStr"/>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
+        </is>
+      </c>
       <c r="E281" t="n">
         <v>27</v>
       </c>
@@ -32104,7 +32108,9 @@
         <v>320</v>
       </c>
       <c r="H281" s="3" t="n"/>
-      <c r="I281" s="3" t="n"/>
+      <c r="I281" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J281" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32112,11 +32118,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="C282" s="2" t="inlineStr">
-        <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
-        </is>
-      </c>
+      <c r="C282" s="2" t="inlineStr"/>
       <c r="E282" t="n">
         <v>27</v>
       </c>
@@ -32125,9 +32127,7 @@
         <v>320</v>
       </c>
       <c r="H282" s="3" t="n"/>
-      <c r="I282" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I282" s="3" t="n"/>
       <c r="J282" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32135,13 +32135,17 @@
       </c>
     </row>
     <row r="283">
-      <c r="C283" s="2" t="inlineStr"/>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>_Autoutilitara basculanta 1+5 locuri cu TMA 3,5 tone-1 buc Documentatie tehnico-economica Racord electricitate si</t>
+        </is>
+      </c>
       <c r="E283" t="n">
         <v>27</v>
       </c>
       <c r="F283" t="inlineStr"/>
       <c r="G283" s="3" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="H283" s="3" t="n"/>
       <c r="I283" s="3" t="n"/>
@@ -32154,7 +32158,7 @@
     <row r="284">
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>_Autoutilitara basculanta 1+5 locuri cu TMA 3,5 tone-1 buc Documentatie tehnico-economica Racord electricitate si</t>
+          <t>apa in sensurile giratorii (E85 Brailei, E85 Cuza Voda, str.Marasesti -Bd.Independentei)</t>
         </is>
       </c>
       <c r="E284" t="n">
@@ -32162,7 +32166,7 @@
       </c>
       <c r="F284" t="inlineStr"/>
       <c r="G284" s="3" t="n">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="H284" s="3" t="n"/>
       <c r="I284" s="3" t="n"/>
@@ -32175,7 +32179,7 @@
     <row r="285">
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>apa in sensurile giratorii (E85 Brailei, E85 Cuza Voda, str.Marasesti -Bd.Independentei)</t>
+          <t>Sistem alarma antiefractie si sistem de supraveghere video</t>
         </is>
       </c>
       <c r="E285" t="n">
@@ -32183,10 +32187,12 @@
       </c>
       <c r="F285" t="inlineStr"/>
       <c r="G285" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H285" s="3" t="n"/>
-      <c r="I285" s="3" t="n"/>
+      <c r="I285" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J285" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32196,7 +32202,7 @@
     <row r="286">
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Sistem alarma antiefractie si sistem de supraveghere video</t>
+          <t>pentru sediu</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -32207,9 +32213,7 @@
         <v>40</v>
       </c>
       <c r="H286" s="3" t="n"/>
-      <c r="I286" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I286" s="3" t="n"/>
       <c r="J286" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32219,7 +32223,7 @@
     <row r="287">
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>pentru sediu</t>
+          <t>COMBUSTIBILI ŞI ENERGIE</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -32227,10 +32231,14 @@
       </c>
       <c r="F287" t="inlineStr"/>
       <c r="G287" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H287" s="3" t="n"/>
-      <c r="I287" s="3" t="n"/>
+        <v>1436.5</v>
+      </c>
+      <c r="H287" s="3" t="n">
+        <v>81.02</v>
+      </c>
+      <c r="I287" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J287" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32240,7 +32248,7 @@
     <row r="288">
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>COMBUSTIBILI ŞI ENERGIE</t>
+          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI</t>
         </is>
       </c>
       <c r="E288" t="n">
@@ -32250,12 +32258,8 @@
       <c r="G288" s="3" t="n">
         <v>1436.5</v>
       </c>
-      <c r="H288" s="3" t="n">
-        <v>81.02</v>
-      </c>
-      <c r="I288" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="H288" s="3" t="n"/>
+      <c r="I288" s="3" t="n"/>
       <c r="J288" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32263,11 +32267,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="C289" s="2" t="inlineStr">
-        <is>
-          <t>PRIMĂRIA MUNICIPIULUI FOCŞANI</t>
-        </is>
-      </c>
+      <c r="C289" s="2" t="inlineStr"/>
       <c r="E289" t="n">
         <v>27</v>
       </c>
@@ -32284,7 +32284,11 @@
       </c>
     </row>
     <row r="290">
-      <c r="C290" s="2" t="inlineStr"/>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>ALTE CHELTUIELI DE INVESTITII</t>
+        </is>
+      </c>
       <c r="E290" t="n">
         <v>27</v>
       </c>
@@ -32303,7 +32307,7 @@
     <row r="291">
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>ALTE CHELTUIELI DE INVESTITII</t>
+          <t>Bransament retele gaze ID</t>
         </is>
       </c>
       <c r="E291" t="n">
@@ -32311,7 +32315,7 @@
       </c>
       <c r="F291" t="inlineStr"/>
       <c r="G291" s="3" t="n">
-        <v>1436.5</v>
+        <v>55</v>
       </c>
       <c r="H291" s="3" t="n"/>
       <c r="I291" s="3" t="n"/>
@@ -32322,11 +32326,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="C292" s="2" t="inlineStr">
-        <is>
-          <t>Bransament retele gaze ID</t>
-        </is>
-      </c>
+      <c r="C292" s="2" t="inlineStr"/>
       <c r="E292" t="n">
         <v>27</v>
       </c>
@@ -32343,16 +32343,22 @@
       </c>
     </row>
     <row r="293">
-      <c r="C293" s="2" t="inlineStr"/>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>Compresor cu surub tip belt 55-08</t>
+        </is>
+      </c>
       <c r="E293" t="n">
         <v>27</v>
       </c>
       <c r="F293" t="inlineStr"/>
       <c r="G293" s="3" t="n">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="H293" s="3" t="n"/>
-      <c r="I293" s="3" t="n"/>
+      <c r="I293" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J293" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32360,11 +32366,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="C294" s="2" t="inlineStr">
-        <is>
-          <t>Compresor cu surub tip belt 55-08</t>
-        </is>
-      </c>
+      <c r="C294" s="2" t="inlineStr"/>
       <c r="E294" t="n">
         <v>27</v>
       </c>
@@ -32373,9 +32375,7 @@
         <v>86</v>
       </c>
       <c r="H294" s="3" t="n"/>
-      <c r="I294" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I294" s="3" t="n"/>
       <c r="J294" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32383,16 +32383,22 @@
       </c>
     </row>
     <row r="295">
-      <c r="C295" s="2" t="inlineStr"/>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>Instalatie tehnologica cu schimb de caldura compabloc CPK 50</t>
+        </is>
+      </c>
       <c r="E295" t="n">
         <v>27</v>
       </c>
       <c r="F295" t="inlineStr"/>
       <c r="G295" s="3" t="n">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="H295" s="3" t="n"/>
-      <c r="I295" s="3" t="n"/>
+      <c r="I295" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J295" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32400,11 +32406,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="C296" s="2" t="inlineStr">
-        <is>
-          <t>Instalatie tehnologica cu schimb de caldura compabloc CPK 50</t>
-        </is>
-      </c>
+      <c r="C296" s="2" t="inlineStr"/>
       <c r="E296" t="n">
         <v>27</v>
       </c>
@@ -32413,9 +32415,7 @@
         <v>29</v>
       </c>
       <c r="H296" s="3" t="n"/>
-      <c r="I296" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I296" s="3" t="n"/>
       <c r="J296" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32423,16 +32423,22 @@
       </c>
     </row>
     <row r="297">
-      <c r="C297" s="2" t="inlineStr"/>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>Instalatie de tratare apa CAF-uri noi</t>
+        </is>
+      </c>
       <c r="E297" t="n">
         <v>27</v>
       </c>
       <c r="F297" t="inlineStr"/>
       <c r="G297" s="3" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="H297" s="3" t="n"/>
-      <c r="I297" s="3" t="n"/>
+      <c r="I297" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J297" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32440,11 +32446,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="C298" s="2" t="inlineStr">
-        <is>
-          <t>Instalatie de tratare apa CAF-uri noi</t>
-        </is>
-      </c>
+      <c r="C298" s="2" t="inlineStr"/>
       <c r="E298" t="n">
         <v>27</v>
       </c>
@@ -32453,9 +32455,7 @@
         <v>6</v>
       </c>
       <c r="H298" s="3" t="n"/>
-      <c r="I298" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I298" s="3" t="n"/>
       <c r="J298" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32469,10 +32469,12 @@
       </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H299" s="3" t="n"/>
-      <c r="I299" s="3" t="n"/>
+      <c r="I299" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J299" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32480,7 +32482,11 @@
       </c>
     </row>
     <row r="300">
-      <c r="C300" s="2" t="inlineStr"/>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>Statie electrica de alimentare 6kv</t>
+        </is>
+      </c>
       <c r="E300" t="n">
         <v>27</v>
       </c>
@@ -32489,9 +32495,7 @@
         <v>10</v>
       </c>
       <c r="H300" s="3" t="n"/>
-      <c r="I300" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I300" s="3" t="n"/>
       <c r="J300" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32501,7 +32505,7 @@
     <row r="301">
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>Statie electrica de alimentare 6kv</t>
+          <t>Retea hidrotehnica alimentare cu apa CET CR</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -32509,10 +32513,12 @@
       </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H301" s="3" t="n"/>
-      <c r="I301" s="3" t="n"/>
+      <c r="I301" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J301" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32520,11 +32526,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="C302" s="2" t="inlineStr">
-        <is>
-          <t>Retea hidrotehnica alimentare cu apa CET CR</t>
-        </is>
-      </c>
+      <c r="C302" s="2" t="inlineStr"/>
       <c r="E302" t="n">
         <v>27</v>
       </c>
@@ -32533,9 +32535,7 @@
         <v>7</v>
       </c>
       <c r="H302" s="3" t="n"/>
-      <c r="I302" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I302" s="3" t="n"/>
       <c r="J302" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32549,7 +32549,7 @@
       </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" s="3" t="n">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="H303" s="3" t="n"/>
       <c r="I303" s="3" t="n"/>
@@ -32560,7 +32560,11 @@
       </c>
     </row>
     <row r="304">
-      <c r="C304" s="2" t="inlineStr"/>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>Retele canalizare</t>
+        </is>
+      </c>
       <c r="E304" t="n">
         <v>27</v>
       </c>
@@ -32577,17 +32581,13 @@
       </c>
     </row>
     <row r="305">
-      <c r="C305" s="2" t="inlineStr">
-        <is>
-          <t>Retele canalizare</t>
-        </is>
-      </c>
+      <c r="C305" s="2" t="inlineStr"/>
       <c r="E305" t="n">
         <v>27</v>
       </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" s="3" t="n">
-        <v>354</v>
+        <v>57</v>
       </c>
       <c r="H305" s="3" t="n"/>
       <c r="I305" s="3" t="n"/>
@@ -32598,7 +32598,11 @@
       </c>
     </row>
     <row r="306">
-      <c r="C306" s="2" t="inlineStr"/>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>Retele termice si A.C.M. aferente bl.H5 str Barsei (152ml)</t>
+        </is>
+      </c>
       <c r="E306" t="n">
         <v>27</v>
       </c>
@@ -32615,17 +32619,13 @@
       </c>
     </row>
     <row r="307">
-      <c r="C307" s="2" t="inlineStr">
-        <is>
-          <t>Retele termice si A.C.M. aferente bl.H5 str Barsei (152ml)</t>
-        </is>
-      </c>
+      <c r="C307" s="2" t="inlineStr"/>
       <c r="E307" t="n">
         <v>27</v>
       </c>
       <c r="F307" t="inlineStr"/>
       <c r="G307" s="3" t="n">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="H307" s="3" t="n"/>
       <c r="I307" s="3" t="n"/>
@@ -32636,7 +32636,11 @@
       </c>
     </row>
     <row r="308">
-      <c r="C308" s="2" t="inlineStr"/>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>Pompa recirculare (2 buc)</t>
+        </is>
+      </c>
       <c r="E308" t="n">
         <v>27</v>
       </c>
@@ -32655,7 +32659,7 @@
     <row r="309">
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>Pompa recirculare (2 buc)</t>
+          <t>Pompa WILO IPL 40/130-2.2</t>
         </is>
       </c>
       <c r="E309" t="n">
@@ -32663,7 +32667,7 @@
       </c>
       <c r="F309" t="inlineStr"/>
       <c r="G309" s="3" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H309" s="3" t="n"/>
       <c r="I309" s="3" t="n"/>
@@ -32674,11 +32678,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="C310" s="2" t="inlineStr">
-        <is>
-          <t>Pompa WILO IPL 40/130-2.2</t>
-        </is>
-      </c>
+      <c r="C310" s="2" t="inlineStr"/>
       <c r="E310" t="n">
         <v>27</v>
       </c>
@@ -32697,11 +32697,11 @@
     <row r="311">
       <c r="C311" s="2" t="inlineStr"/>
       <c r="E311" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F311" t="inlineStr"/>
       <c r="G311" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H311" s="3" t="n"/>
       <c r="I311" s="3" t="n"/>
@@ -32712,7 +32712,11 @@
       </c>
     </row>
     <row r="312">
-      <c r="C312" s="2" t="inlineStr"/>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>Pompa WILO IPL 32/125-1.1/2</t>
+        </is>
+      </c>
       <c r="E312" t="n">
         <v>28</v>
       </c>
@@ -32729,17 +32733,13 @@
       </c>
     </row>
     <row r="313">
-      <c r="C313" s="2" t="inlineStr">
-        <is>
-          <t>Pompa WILO IPL 32/125-1.1/2</t>
-        </is>
-      </c>
+      <c r="C313" s="2" t="inlineStr"/>
       <c r="E313" t="n">
         <v>28</v>
       </c>
       <c r="F313" t="inlineStr"/>
       <c r="G313" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H313" s="3" t="n"/>
       <c r="I313" s="3" t="n"/>
@@ -32750,7 +32750,11 @@
       </c>
     </row>
     <row r="314">
-      <c r="C314" s="2" t="inlineStr"/>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>Instalatie pompare recirculare A.C.C. in PT nr.53</t>
+        </is>
+      </c>
       <c r="E314" t="n">
         <v>28</v>
       </c>
@@ -32769,7 +32773,7 @@
     <row r="315">
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>Instalatie pompare recirculare A.C.C. in PT nr.53</t>
+          <t>Electropompa centrifuga monoetajata L-IVE-4P 125-250-</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -32777,10 +32781,12 @@
       </c>
       <c r="F315" t="inlineStr"/>
       <c r="G315" s="3" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H315" s="3" t="n"/>
-      <c r="I315" s="3" t="n"/>
+      <c r="I315" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J315" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32790,7 +32796,7 @@
     <row r="316">
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Electropompa centrifuga monoetajata L-IVE-4P 125-250-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="E316" t="n">
@@ -32801,9 +32807,7 @@
         <v>21</v>
       </c>
       <c r="H316" s="3" t="n"/>
-      <c r="I316" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I316" s="3" t="n"/>
       <c r="J316" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32813,7 +32817,7 @@
     <row r="317">
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>Electropompa centrifuga monoetajata L-IVE-2P 80-160-</t>
         </is>
       </c>
       <c r="E317" t="n">
@@ -32821,10 +32825,12 @@
       </c>
       <c r="F317" t="inlineStr"/>
       <c r="G317" s="3" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H317" s="3" t="n"/>
-      <c r="I317" s="3" t="n"/>
+      <c r="I317" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J317" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32834,7 +32840,7 @@
     <row r="318">
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Electropompa centrifuga monoetajata L-IVE-2P 80-160-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="E318" t="n">
@@ -32845,9 +32851,7 @@
         <v>13</v>
       </c>
       <c r="H318" s="3" t="n"/>
-      <c r="I318" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I318" s="3" t="n"/>
       <c r="J318" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32857,7 +32861,7 @@
     <row r="319">
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>Electropompa centrifuga monoetajata L-IVE-2P 40-125S-</t>
         </is>
       </c>
       <c r="E319" t="n">
@@ -32865,7 +32869,7 @@
       </c>
       <c r="F319" t="inlineStr"/>
       <c r="G319" s="3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H319" s="3" t="n"/>
       <c r="I319" s="3" t="n"/>
@@ -32878,7 +32882,7 @@
     <row r="320">
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Electropompa centrifuga monoetajata L-IVE-2P 40-125S-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="E320" t="n">
@@ -32899,7 +32903,7 @@
     <row r="321">
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>Retele termice si A.C.M. locuinte sociale str. Cpt Cretu</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -32907,10 +32911,12 @@
       </c>
       <c r="F321" t="inlineStr"/>
       <c r="G321" s="3" t="n">
-        <v>8</v>
+        <v>195</v>
       </c>
       <c r="H321" s="3" t="n"/>
-      <c r="I321" s="3" t="n"/>
+      <c r="I321" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J321" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32920,7 +32926,7 @@
     <row r="322">
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Retele termice si A.C.M. locuinte sociale str. Cpt Cretu</t>
+          <t>Florin</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -32931,9 +32937,7 @@
         <v>195</v>
       </c>
       <c r="H322" s="3" t="n"/>
-      <c r="I322" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I322" s="3" t="n"/>
       <c r="J322" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -32943,7 +32947,7 @@
     <row r="323">
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>Florin</t>
+          <t>Alimentare cu energie termica din sistemul centralizat al</t>
         </is>
       </c>
       <c r="E323" t="n">
@@ -32951,7 +32955,7 @@
       </c>
       <c r="F323" t="inlineStr"/>
       <c r="G323" s="3" t="n">
-        <v>195</v>
+        <v>38</v>
       </c>
       <c r="H323" s="3" t="n"/>
       <c r="I323" s="3" t="n"/>
@@ -32964,7 +32968,7 @@
     <row r="324">
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Alimentare cu energie termica din sistemul centralizat al</t>
+          <t>imobilului din str. Cuza Voda nr. 43</t>
         </is>
       </c>
       <c r="E324" t="n">
@@ -32983,17 +32987,13 @@
       </c>
     </row>
     <row r="325">
-      <c r="C325" s="2" t="inlineStr">
-        <is>
-          <t>imobilului din str. Cuza Voda nr. 43</t>
-        </is>
-      </c>
+      <c r="C325" s="2" t="inlineStr"/>
       <c r="E325" t="n">
         <v>28</v>
       </c>
       <c r="F325" t="inlineStr"/>
       <c r="G325" s="3" t="n">
-        <v>38</v>
+        <v>137</v>
       </c>
       <c r="H325" s="3" t="n"/>
       <c r="I325" s="3" t="n"/>
@@ -33004,7 +33004,11 @@
       </c>
     </row>
     <row r="326">
-      <c r="C326" s="2" t="inlineStr"/>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>Teren 576 mp</t>
+        </is>
+      </c>
       <c r="E326" t="n">
         <v>28</v>
       </c>
@@ -33023,7 +33027,7 @@
     <row r="327">
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>Teren 576 mp</t>
+          <t>Pompa recirculare 02000155-ETL 032-032-160</t>
         </is>
       </c>
       <c r="E327" t="n">
@@ -33031,7 +33035,7 @@
       </c>
       <c r="F327" t="inlineStr"/>
       <c r="G327" s="3" t="n">
-        <v>137</v>
+        <v>6</v>
       </c>
       <c r="H327" s="3" t="n"/>
       <c r="I327" s="3" t="n"/>
@@ -33044,7 +33048,7 @@
     <row r="328">
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Pompa recirculare 02000155-ETL 032-032-160</t>
+          <t>Boiler termoelectric cu o serpentina 1000l 12kW montaj pardoseala</t>
         </is>
       </c>
       <c r="E328" t="n">
@@ -33052,7 +33056,7 @@
       </c>
       <c r="F328" t="inlineStr"/>
       <c r="G328" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H328" s="3" t="n"/>
       <c r="I328" s="3" t="n"/>
@@ -33069,7 +33073,7 @@
       </c>
       <c r="F329" t="inlineStr"/>
       <c r="G329" s="3" t="n">
-        <v>6009</v>
+        <v>39</v>
       </c>
       <c r="H329" s="3" t="n"/>
       <c r="I329" s="3" t="n"/>
@@ -33082,7 +33086,7 @@
     <row r="330">
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Boiler termoelectric cu o serpentina 1000l 12kW montaj pardoseala</t>
+          <t>Foraj PUT incinta</t>
         </is>
       </c>
       <c r="E330" t="n">
@@ -33090,7 +33094,7 @@
       </c>
       <c r="F330" t="inlineStr"/>
       <c r="G330" s="3" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="H330" s="3" t="n"/>
       <c r="I330" s="3" t="n"/>
@@ -33101,16 +33105,22 @@
       </c>
     </row>
     <row r="331">
-      <c r="C331" s="2" t="inlineStr"/>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>Stivuitor manuale capacitate 2000kg, inaltime ridicare 2000</t>
+        </is>
+      </c>
       <c r="E331" t="n">
         <v>28</v>
       </c>
       <c r="F331" t="inlineStr"/>
       <c r="G331" s="3" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="H331" s="3" t="n"/>
-      <c r="I331" s="3" t="n"/>
+      <c r="I331" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J331" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -33120,7 +33130,7 @@
     <row r="332">
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Foraj PUT incinta</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E332" t="n">
@@ -33128,7 +33138,7 @@
       </c>
       <c r="F332" t="inlineStr"/>
       <c r="G332" s="3" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="H332" s="3" t="n"/>
       <c r="I332" s="3" t="n"/>
@@ -33139,17 +33149,13 @@
       </c>
     </row>
     <row r="333">
-      <c r="C333" s="2" t="inlineStr">
-        <is>
-          <t>Stivuitor manuale capacitate 2000kg, inaltime ridicare 2000</t>
-        </is>
-      </c>
+      <c r="C333" s="2" t="inlineStr"/>
       <c r="E333" t="n">
         <v>28</v>
       </c>
       <c r="F333" t="inlineStr"/>
       <c r="G333" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H333" s="3" t="n"/>
       <c r="I333" s="3" t="n">
@@ -33164,7 +33170,7 @@
     <row r="334">
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>Cuva HDPE 1600*100*700mm 5mm grosime</t>
         </is>
       </c>
       <c r="E334" t="n">
@@ -33172,7 +33178,7 @@
       </c>
       <c r="F334" t="inlineStr"/>
       <c r="G334" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H334" s="3" t="n"/>
       <c r="I334" s="3" t="n"/>
@@ -33183,13 +33189,17 @@
       </c>
     </row>
     <row r="335">
-      <c r="C335" s="2" t="inlineStr"/>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>Pompa centrifugala MN 32-200C, 3*380V</t>
+        </is>
+      </c>
       <c r="E335" t="n">
         <v>28</v>
       </c>
       <c r="F335" t="inlineStr"/>
       <c r="G335" s="3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H335" s="3" t="n"/>
       <c r="I335" s="3" t="n">
@@ -33202,17 +33212,13 @@
       </c>
     </row>
     <row r="336">
-      <c r="C336" s="2" t="inlineStr">
-        <is>
-          <t>Cuva HDPE 1600*100*700mm 5mm grosime</t>
-        </is>
-      </c>
+      <c r="C336" s="2" t="inlineStr"/>
       <c r="E336" t="n">
         <v>28</v>
       </c>
       <c r="F336" t="inlineStr"/>
       <c r="G336" s="3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H336" s="3" t="n"/>
       <c r="I336" s="3" t="n"/>
@@ -33225,7 +33231,7 @@
     <row r="337">
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>Pompa centrifugala MN 32-200C, 3*380V</t>
+          <t>Modul Dashboard monitorizare parametrii</t>
         </is>
       </c>
       <c r="E337" t="n">
@@ -33233,12 +33239,10 @@
       </c>
       <c r="F337" t="inlineStr"/>
       <c r="G337" s="3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="H337" s="3" t="n"/>
-      <c r="I337" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="I337" s="3" t="n"/>
       <c r="J337" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -33252,7 +33256,7 @@
       </c>
       <c r="F338" t="inlineStr"/>
       <c r="G338" s="3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="H338" s="3" t="n"/>
       <c r="I338" s="3" t="n"/>
@@ -33265,7 +33269,7 @@
     <row r="339">
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>Modul Dashboard monitorizare parametrii</t>
+          <t>Licente pentru ansamblu de trasmisie date on-line</t>
         </is>
       </c>
       <c r="E339" t="n">
@@ -33273,10 +33277,12 @@
       </c>
       <c r="F339" t="inlineStr"/>
       <c r="G339" s="3" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H339" s="3" t="n"/>
-      <c r="I339" s="3" t="n"/>
+      <c r="I339" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J339" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -33290,7 +33296,7 @@
       </c>
       <c r="F340" t="inlineStr"/>
       <c r="G340" s="3" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H340" s="3" t="n"/>
       <c r="I340" s="3" t="n"/>
@@ -33303,7 +33309,7 @@
     <row r="341">
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>Licente pentru ansamblu de trasmisie date on-line</t>
+          <t>Ansamblu de trasmisie date on-line</t>
         </is>
       </c>
       <c r="E341" t="n">
@@ -33311,7 +33317,7 @@
       </c>
       <c r="F341" t="inlineStr"/>
       <c r="G341" s="3" t="n">
-        <v>24</v>
+        <v>296</v>
       </c>
       <c r="H341" s="3" t="n"/>
       <c r="I341" s="3" t="n">
@@ -33330,7 +33336,7 @@
       </c>
       <c r="F342" t="inlineStr"/>
       <c r="G342" s="3" t="n">
-        <v>24</v>
+        <v>296</v>
       </c>
       <c r="H342" s="3" t="n"/>
       <c r="I342" s="3" t="n"/>
@@ -33343,7 +33349,7 @@
     <row r="343">
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>Ansamblu de trasmisie date on-line</t>
+          <t>TRANSPORTURI</t>
         </is>
       </c>
       <c r="E343" t="n">
@@ -33351,12 +33357,12 @@
       </c>
       <c r="F343" t="inlineStr"/>
       <c r="G343" s="3" t="n">
-        <v>296</v>
-      </c>
-      <c r="H343" s="3" t="n"/>
-      <c r="I343" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>63543.81</v>
+      </c>
+      <c r="H343" s="3" t="n">
+        <v>84.02</v>
+      </c>
+      <c r="I343" s="3" t="n"/>
       <c r="J343" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -33364,13 +33370,17 @@
       </c>
     </row>
     <row r="344">
-      <c r="C344" s="2" t="inlineStr"/>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>1 PRIMĂRIA MUNICIPIULUI FOCŞANI ⅡI</t>
+        </is>
+      </c>
       <c r="E344" t="n">
         <v>28</v>
       </c>
       <c r="F344" t="inlineStr"/>
       <c r="G344" s="3" t="n">
-        <v>296</v>
+        <v>63543.81</v>
       </c>
       <c r="H344" s="3" t="n"/>
       <c r="I344" s="3" t="n"/>
@@ -33381,22 +33391,18 @@
       </c>
     </row>
     <row r="345">
-      <c r="C345" s="2" t="inlineStr">
-        <is>
-          <t>TRANSPORTURI</t>
-        </is>
-      </c>
+      <c r="C345" s="2" t="inlineStr"/>
       <c r="E345" t="n">
         <v>28</v>
       </c>
       <c r="F345" t="inlineStr"/>
       <c r="G345" s="3" t="n">
-        <v>63543.81</v>
-      </c>
-      <c r="H345" s="3" t="n">
-        <v>84.02</v>
-      </c>
-      <c r="I345" s="3" t="n"/>
+        <v>2032.86</v>
+      </c>
+      <c r="H345" s="3" t="n"/>
+      <c r="I345" s="3" t="n">
+        <v>2708.68</v>
+      </c>
       <c r="J345" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -33406,7 +33412,7 @@
     <row r="346">
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>1 PRIMĂRIA MUNICIPIULUI FOCŞANI ⅡI</t>
+          <t>Refacere infrastructură str.Ion Basgan</t>
         </is>
       </c>
       <c r="E346" t="n">
@@ -33414,7 +33420,7 @@
       </c>
       <c r="F346" t="inlineStr"/>
       <c r="G346" s="3" t="n">
-        <v>63543.81</v>
+        <v>2032.86</v>
       </c>
       <c r="H346" s="3" t="n"/>
       <c r="I346" s="3" t="n"/>
@@ -33425,17 +33431,19 @@
       </c>
     </row>
     <row r="347">
-      <c r="C347" s="2" t="inlineStr"/>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>Amplasare, montare si punere in functiune a 5 statii de reincarcare masini electrice (AFM)</t>
+        </is>
+      </c>
       <c r="E347" t="n">
         <v>28</v>
       </c>
       <c r="F347" t="inlineStr"/>
-      <c r="G347" s="3" t="n">
-        <v>2032.86</v>
-      </c>
+      <c r="G347" s="3" t="n"/>
       <c r="H347" s="3" t="n"/>
       <c r="I347" s="3" t="n">
-        <v>2708.68</v>
+        <v>11160.92</v>
       </c>
       <c r="J347" t="inlineStr">
         <is>
@@ -33446,7 +33454,7 @@
     <row r="348">
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Refacere infrastructură str.Ion Basgan</t>
+          <t>Refacere infrastructura strazi, sistematizare verticala str. Timis, str. N. Balcescu, str. Predeal (tronson cuprins intre</t>
         </is>
       </c>
       <c r="E348" t="n">
@@ -33454,7 +33462,7 @@
       </c>
       <c r="F348" t="inlineStr"/>
       <c r="G348" s="3" t="n">
-        <v>2032.86</v>
+        <v>4333.16</v>
       </c>
       <c r="H348" s="3" t="n"/>
       <c r="I348" s="3" t="n"/>
@@ -33467,18 +33475,18 @@
     <row r="349">
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>Amplasare, montare si punere in functiune a 5 statii de reincarcare masini electrice (AFM)</t>
+          <t>strada lon Creanga si Grigore lonescu) și reparații si așternere covoare asfaltice carosabil str.Magazia Garii</t>
         </is>
       </c>
       <c r="E349" t="n">
         <v>28</v>
       </c>
       <c r="F349" t="inlineStr"/>
-      <c r="G349" s="3" t="n"/>
+      <c r="G349" s="3" t="n">
+        <v>4333.16</v>
+      </c>
       <c r="H349" s="3" t="n"/>
-      <c r="I349" s="3" t="n">
-        <v>11160.92</v>
-      </c>
+      <c r="I349" s="3" t="n"/>
       <c r="J349" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -33488,15 +33496,15 @@
     <row r="350">
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Refacere infrastructura strazi, sistematizare verticala str. Timis, str. N. Balcescu, str. Predeal (tronson cuprins intre</t>
+          <t>Refacere infrastructura stradala si parcari adiacente strazilor Maior Gh. Pastia, M. Kogalniceanu, D. Cantemir,</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F350" t="inlineStr"/>
       <c r="G350" s="3" t="n">
-        <v>4333.16</v>
+        <v>2820.17</v>
       </c>
       <c r="H350" s="3" t="n"/>
       <c r="I350" s="3" t="n"/>
@@ -33509,18 +33517,20 @@
     <row r="351">
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>strada lon Creanga si Grigore lonescu) și reparații si așternere covoare asfaltice carosabil str.Magazia Garii</t>
+          <t>Cuza Voda - PT8</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F351" t="inlineStr"/>
       <c r="G351" s="3" t="n">
-        <v>4333.16</v>
+        <v>2820.17</v>
       </c>
       <c r="H351" s="3" t="n"/>
-      <c r="I351" s="3" t="n"/>
+      <c r="I351" s="3" t="n">
+        <v>2820.18</v>
+      </c>
       <c r="J351" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -33530,7 +33540,7 @@
     <row r="352">
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Refacere infrastructura stradala si parcari adiacente strazilor Maior Gh. Pastia, M. Kogalniceanu, D. Cantemir,</t>
+          <t>Refacere infrastructura strazi, sistematizare verticala str. Prof. C. Stere, str. Ecaterina Varga, str. Bujor, str. Agriculturii, str.Muresului,str. Cernei, str.Dogariei,</t>
         </is>
       </c>
       <c r="E352" t="n">
@@ -33538,10 +33548,12 @@
       </c>
       <c r="F352" t="inlineStr"/>
       <c r="G352" s="3" t="n">
-        <v>2820.17</v>
+        <v>14331.46</v>
       </c>
       <c r="H352" s="3" t="n"/>
-      <c r="I352" s="3" t="n"/>
+      <c r="I352" s="3" t="n">
+        <v>14331.47</v>
+      </c>
       <c r="J352" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -33551,7 +33563,7 @@
     <row r="353">
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>Cuza Voda - PT8</t>
+          <t>str.Crisana, str.Greva de la Grivita</t>
         </is>
       </c>
       <c r="E353" t="n">
@@ -33559,12 +33571,10 @@
       </c>
       <c r="F353" t="inlineStr"/>
       <c r="G353" s="3" t="n">
-        <v>2820.17</v>
+        <v>14331.46</v>
       </c>
       <c r="H353" s="3" t="n"/>
-      <c r="I353" s="3" t="n">
-        <v>2820.18</v>
-      </c>
+      <c r="I353" s="3" t="n"/>
       <c r="J353" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -33574,7 +33584,7 @@
     <row r="354">
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Refacere infrastructura strazi, sistematizare verticala str. Prof. C. Stere, str. Ecaterina Varga, str. Bujor, str. Agriculturii, str.Muresului,str. Cernei, str.Dogariei,</t>
+          <t>Refacere infrastructura str.Alecu Sihleanu si fundatura, str.Maior G. Sonțu si fundatura, str. Aviatorilor, Aleea Cuza</t>
         </is>
       </c>
       <c r="E354" t="n">
@@ -33582,11 +33592,11 @@
       </c>
       <c r="F354" t="inlineStr"/>
       <c r="G354" s="3" t="n">
-        <v>14331.46</v>
+        <v>10044.2</v>
       </c>
       <c r="H354" s="3" t="n"/>
       <c r="I354" s="3" t="n">
-        <v>14331.47</v>
+        <v>10044.2</v>
       </c>
       <c r="J354" t="inlineStr">
         <is>
@@ -33597,7 +33607,7 @@
     <row r="355">
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>str.Crisana, str.Greva de la Grivita</t>
+          <t>Voda și fundatura</t>
         </is>
       </c>
       <c r="E355" t="n">
@@ -33605,7 +33615,7 @@
       </c>
       <c r="F355" t="inlineStr"/>
       <c r="G355" s="3" t="n">
-        <v>14331.46</v>
+        <v>10044.2</v>
       </c>
       <c r="H355" s="3" t="n"/>
       <c r="I355" s="3" t="n"/>
@@ -33618,7 +33628,7 @@
     <row r="356">
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Refacere infrastructura str.Alecu Sihleanu si fundatura, str.Maior G. Sonțu si fundatura, str. Aviatorilor, Aleea Cuza</t>
+          <t>Refacere infrastructura strazi, sistematizare verticala str.</t>
         </is>
       </c>
       <c r="E356" t="n">
@@ -33626,12 +33636,10 @@
       </c>
       <c r="F356" t="inlineStr"/>
       <c r="G356" s="3" t="n">
-        <v>10044.2</v>
+        <v>8399.190000000001</v>
       </c>
       <c r="H356" s="3" t="n"/>
-      <c r="I356" s="3" t="n">
-        <v>10044.2</v>
-      </c>
+      <c r="I356" s="3" t="n"/>
       <c r="J356" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -33641,7 +33649,7 @@
     <row r="357">
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>Voda și fundatura</t>
+          <t>Fagaras, str. Gh. Potop, str. Ghioceilor, str.Arges, str.Dinicu Golescu, str.Zorilor,P-ta Victoriei</t>
         </is>
       </c>
       <c r="E357" t="n">
@@ -33649,10 +33657,12 @@
       </c>
       <c r="F357" t="inlineStr"/>
       <c r="G357" s="3" t="n">
-        <v>10044.2</v>
+        <v>8399.190000000001</v>
       </c>
       <c r="H357" s="3" t="n"/>
-      <c r="I357" s="3" t="n"/>
+      <c r="I357" s="3" t="n">
+        <v>8399.190000000001</v>
+      </c>
       <c r="J357" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -33662,7 +33672,7 @@
     <row r="358">
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Refacere infrastructura strazi, sistematizare verticala str.</t>
+          <t>Refacere infrastructură strazi, sistematizare verticala,parcari, spatii verzi si accese pentru str. N. lorga, str. Oituz (tronson cuprins între str. Marasti și str. D.</t>
         </is>
       </c>
       <c r="E358" t="n">
@@ -33670,10 +33680,12 @@
       </c>
       <c r="F358" t="inlineStr"/>
       <c r="G358" s="3" t="n">
-        <v>8399.190000000001</v>
+        <v>4551.76</v>
       </c>
       <c r="H358" s="3" t="n"/>
-      <c r="I358" s="3" t="n"/>
+      <c r="I358" s="3" t="n">
+        <v>5837.8</v>
+      </c>
       <c r="J358" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -33683,7 +33695,7 @@
     <row r="359">
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>Fagaras, str. Gh. Potop, str. Ghioceilor, str.Arges, str.Dinicu Golescu, str.Zorilor,P-ta Victoriei</t>
+          <t>Zamfirescu), str. Miorita, str.Stefan cel Mare , str.Eroilor, str.Vamii</t>
         </is>
       </c>
       <c r="E359" t="n">
@@ -33691,12 +33703,10 @@
       </c>
       <c r="F359" t="inlineStr"/>
       <c r="G359" s="3" t="n">
-        <v>8399.190000000001</v>
+        <v>4551.76</v>
       </c>
       <c r="H359" s="3" t="n"/>
-      <c r="I359" s="3" t="n">
-        <v>8399.190000000001</v>
-      </c>
+      <c r="I359" s="3" t="n"/>
       <c r="J359" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -33706,7 +33716,7 @@
     <row r="360">
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>Refacere infrastructură strazi, sistematizare verticala,parcari, spatii verzi si accese pentru str. N. lorga, str. Oituz (tronson cuprins între str. Marasti și str. D.</t>
+          <t>zona Bahne, str. Cezar Bolliac(tronson cuprins intre str. Cuza Voda si str. Lupeni), str.Doctor Telemac, str. Rarau, str. Dornei, str. Pictor Grigorescu(tronson cuprins intre str.</t>
         </is>
       </c>
       <c r="E360" t="n">
@@ -33714,11 +33724,11 @@
       </c>
       <c r="F360" t="inlineStr"/>
       <c r="G360" s="3" t="n">
-        <v>4551.76</v>
+        <v>13526.09</v>
       </c>
       <c r="H360" s="3" t="n"/>
       <c r="I360" s="3" t="n">
-        <v>5837.8</v>
+        <v>13526.09</v>
       </c>
       <c r="J360" t="inlineStr">
         <is>
@@ -33729,7 +33739,7 @@
     <row r="361">
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>Zamfirescu), str. Miorita, str.Stefan cel Mare , str.Eroilor, str.Vamii</t>
+          <t>Al.Vlahuta si str. Panduri), Aleea Caminului, str. Al.Vlahuta, str. Lupeni (tronson cuprins intre str. Cezar Bolliac si Aleea ALTE CHELTUIELI DE INVESTITII</t>
         </is>
       </c>
       <c r="E361" t="n">
@@ -33737,7 +33747,7 @@
       </c>
       <c r="F361" t="inlineStr"/>
       <c r="G361" s="3" t="n">
-        <v>4551.76</v>
+        <v>13526.09</v>
       </c>
       <c r="H361" s="3" t="n"/>
       <c r="I361" s="3" t="n"/>
@@ -33750,7 +33760,7 @@
     <row r="362">
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>zona Bahne, str. Cezar Bolliac(tronson cuprins intre str. Cuza Voda si str. Lupeni), str.Doctor Telemac, str. Rarau, str. Dornei, str. Pictor Grigorescu(tronson cuprins intre str.</t>
+          <t>Documentatie tehnico-economica ,,Amenajare si</t>
         </is>
       </c>
       <c r="E362" t="n">
@@ -33758,12 +33768,10 @@
       </c>
       <c r="F362" t="inlineStr"/>
       <c r="G362" s="3" t="n">
-        <v>13526.09</v>
+        <v>90</v>
       </c>
       <c r="H362" s="3" t="n"/>
-      <c r="I362" s="3" t="n">
-        <v>13526.09</v>
-      </c>
+      <c r="I362" s="3" t="n"/>
       <c r="J362" t="inlineStr">
         <is>
           <t>ocr</t>
@@ -33773,7 +33781,7 @@
     <row r="363">
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>Al.Vlahuta si str. Panduri), Aleea Caminului, str. Al.Vlahuta, str. Lupeni (tronson cuprins intre str. Cezar Bolliac si Aleea ALTE CHELTUIELI DE INVESTITII</t>
+          <t>modernizare zone parcare din Municipiul Focsani"</t>
         </is>
       </c>
       <c r="E363" t="n">
@@ -33781,7 +33789,7 @@
       </c>
       <c r="F363" t="inlineStr"/>
       <c r="G363" s="3" t="n">
-        <v>13526.09</v>
+        <v>90</v>
       </c>
       <c r="H363" s="3" t="n"/>
       <c r="I363" s="3" t="n"/>
@@ -33794,7 +33802,7 @@
     <row r="364">
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica ,,Amenajare si</t>
+          <t>Documentatie tehnico-economica ,,Reabilitare suprafata</t>
         </is>
       </c>
       <c r="E364" t="n">
@@ -33802,7 +33810,7 @@
       </c>
       <c r="F364" t="inlineStr"/>
       <c r="G364" s="3" t="n">
-        <v>90</v>
+        <v>2000</v>
       </c>
       <c r="H364" s="3" t="n"/>
       <c r="I364" s="3" t="n"/>
@@ -33815,7 +33823,7 @@
     <row r="365">
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>modernizare zone parcare din Municipiul Focsani"</t>
+          <t>carosabila Calea Moldovei - Calea Munteniei"</t>
         </is>
       </c>
       <c r="E365" t="n">
@@ -33823,7 +33831,7 @@
       </c>
       <c r="F365" t="inlineStr"/>
       <c r="G365" s="3" t="n">
-        <v>90</v>
+        <v>2000</v>
       </c>
       <c r="H365" s="3" t="n"/>
       <c r="I365" s="3" t="n"/>
@@ -33836,7 +33844,7 @@
     <row r="366">
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica ,,Reabilitare suprafata</t>
+          <t>Documentatie tehnico-economica Construire drum acces</t>
         </is>
       </c>
       <c r="E366" t="n">
@@ -33844,7 +33852,7 @@
       </c>
       <c r="F366" t="inlineStr"/>
       <c r="G366" s="3" t="n">
-        <v>2000</v>
+        <v>50</v>
       </c>
       <c r="H366" s="3" t="n"/>
       <c r="I366" s="3" t="n"/>
@@ -33857,7 +33865,7 @@
     <row r="367">
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>carosabila Calea Moldovei - Calea Munteniei"</t>
+          <t>pe teren C.F. nr.61771 (MAPN)</t>
         </is>
       </c>
       <c r="E367" t="n">
@@ -33865,7 +33873,7 @@
       </c>
       <c r="F367" t="inlineStr"/>
       <c r="G367" s="3" t="n">
-        <v>2000</v>
+        <v>50</v>
       </c>
       <c r="H367" s="3" t="n"/>
       <c r="I367" s="3" t="n"/>
@@ -33878,7 +33886,7 @@
     <row r="368">
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica Construire drum acces</t>
+          <t>Actualizare documentatie tehnico-economica Reabilitare</t>
         </is>
       </c>
       <c r="E368" t="n">
@@ -33886,7 +33894,7 @@
       </c>
       <c r="F368" t="inlineStr"/>
       <c r="G368" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H368" s="3" t="n"/>
       <c r="I368" s="3" t="n"/>
@@ -33899,7 +33907,7 @@
     <row r="369">
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>pe teren C.F. nr.61771 (MAPN)</t>
+          <t>Pasaj pe str. Marasesti (DN 2D km+223) peste magistrala CF 500 Buzau -Marasesti in mun Focsani</t>
         </is>
       </c>
       <c r="E369" t="n">
@@ -33907,7 +33915,7 @@
       </c>
       <c r="F369" t="inlineStr"/>
       <c r="G369" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H369" s="3" t="n"/>
       <c r="I369" s="3" t="n"/>
@@ -33920,7 +33928,7 @@
     <row r="370">
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Actualizare documentatie tehnico-economica Reabilitare</t>
+          <t>Documentatie tehnico-economica-Construire sistem de</t>
         </is>
       </c>
       <c r="E370" t="n">
@@ -33928,7 +33936,7 @@
       </c>
       <c r="F370" t="inlineStr"/>
       <c r="G370" s="3" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H370" s="3" t="n"/>
       <c r="I370" s="3" t="n"/>
@@ -33941,7 +33949,7 @@
     <row r="371">
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>Pasaj pe str. Marasesti (DN 2D km+223) peste magistrala CF 500 Buzau -Marasesti in mun Focsani</t>
+          <t>gestionare ape pluviale in Pasaj Valcele</t>
         </is>
       </c>
       <c r="E371" t="n">
@@ -33949,7 +33957,7 @@
       </c>
       <c r="F371" t="inlineStr"/>
       <c r="G371" s="3" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H371" s="3" t="n"/>
       <c r="I371" s="3" t="n"/>
@@ -33962,7 +33970,7 @@
     <row r="372">
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Documentatie tehnico-economica-Construire sistem de</t>
+          <t>DIRECTIA DE DEZVOLTARE SERVICII PUBLICE</t>
         </is>
       </c>
       <c r="E372" t="n">
@@ -33970,7 +33978,7 @@
       </c>
       <c r="F372" t="inlineStr"/>
       <c r="G372" s="3" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="H372" s="3" t="n"/>
       <c r="I372" s="3" t="n"/>
@@ -33981,17 +33989,13 @@
       </c>
     </row>
     <row r="373">
-      <c r="C373" s="2" t="inlineStr">
-        <is>
-          <t>gestionare ape pluviale in Pasaj Valcele</t>
-        </is>
-      </c>
+      <c r="C373" s="2" t="inlineStr"/>
       <c r="E373" t="n">
         <v>29</v>
       </c>
       <c r="F373" t="inlineStr"/>
       <c r="G373" s="3" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="H373" s="3" t="n"/>
       <c r="I373" s="3" t="n"/>
@@ -34004,7 +34008,7 @@
     <row r="374">
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>DIRECTIA DE DEZVOLTARE SERVICII PUBLICE</t>
+          <t>A ALTE CHELTUIELI DE INVESTITII</t>
         </is>
       </c>
       <c r="E374" t="n">
@@ -34040,11 +34044,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="C376" s="2" t="inlineStr">
-        <is>
-          <t>A ALTE CHELTUIELI DE INVESTITII</t>
-        </is>
-      </c>
+      <c r="C376" s="2" t="inlineStr"/>
       <c r="E376" t="n">
         <v>29</v>
       </c>
@@ -34061,7 +34061,11 @@
       </c>
     </row>
     <row r="377">
-      <c r="C377" s="2" t="inlineStr"/>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>Masina de marcaj rutier</t>
+        </is>
+      </c>
       <c r="E377" t="n">
         <v>29</v>
       </c>
@@ -34072,44 +34076,6 @@
       <c r="H377" s="3" t="n"/>
       <c r="I377" s="3" t="n"/>
       <c r="J377" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="C378" s="2" t="inlineStr"/>
-      <c r="E378" t="n">
-        <v>29</v>
-      </c>
-      <c r="F378" t="inlineStr"/>
-      <c r="G378" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="H378" s="3" t="n"/>
-      <c r="I378" s="3" t="n"/>
-      <c r="J378" t="inlineStr">
-        <is>
-          <t>ocr</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="C379" s="2" t="inlineStr">
-        <is>
-          <t>Masina de marcaj rutier</t>
-        </is>
-      </c>
-      <c r="E379" t="n">
-        <v>29</v>
-      </c>
-      <c r="F379" t="inlineStr"/>
-      <c r="G379" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="H379" s="3" t="n"/>
-      <c r="I379" s="3" t="n"/>
-      <c r="J379" t="inlineStr">
         <is>
           <t>ocr</t>
         </is>
@@ -34287,7 +34253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -34333,12 +34299,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -34356,19 +34322,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 03.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>03.02 total_2026: parent 353,00 != sum(children) 1,89 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -34386,19 +34352,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 16.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>16.02 total_2026: parent 10,54 != sum(children) 74,47 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -34416,19 +34382,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 33.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>33.02 total_2026: parent 1,32 != sum(children) 275,04 (5 children)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -34446,19 +34412,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 35.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>35.02 total_2026: parent 3,97 != sum(children) 773,20 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -34476,14 +34442,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 42.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>42.02 total_2026: parent 11,42 != sum(children) 361,07 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -34492,28 +34458,23 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>54.02</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 54.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (55%): 'SUBVENTII PENTRU INVESTITII' vs 'Subventii de la bugetul de stat'</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -34522,28 +34483,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>42.02.69</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 61.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (36%): 'Sume BS cofinantare proiecte UE 2014-202' vs 'Subvenţii de la bugetul de stat către bu'</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -34552,28 +34508,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>42.02.93</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 66.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (36%): 'Sume BS cofinantare proiecte UE 2021-202' vs 'Subvenţii de la bugetul de stat necesare'</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -34582,28 +34533,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>45.02</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 68.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (50%): 'SUME DE PRIMIT DE LA UE 2021-2027' vs 'Sume primite de la UE/alti donatori în c'</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -34612,41 +34558,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 70.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -34656,87 +34597,82 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 74.02 total_2026: still inconsistent — UNRESOLVED</t>
+          <t>54.02 total_2026: parent 6,14 != sum(children) 2,30 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p5: 0 cells recovered</t>
+          <t>duplicate of p5 with different values</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>03.02</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>03.02 total_2026: parent 353,00 != sum(children) 1,89 (1 children)</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16.02</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16.02 total_2026: parent 10,54 != sum(children) 74,47 (3 children)</t>
+          <t>name mismatch vs nomenclator (25%): 'Dobanzi' vs 'Tranzactii privind datoria publica si im'</t>
         </is>
       </c>
     </row>
@@ -34752,11 +34688,11 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -34766,117 +34702,112 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33.02 total_2026: parent 1,32 != sum(children) 275,04 (5 children)</t>
+          <t>61.02 total_2026: parent 11,40 != sum(children) 250,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>35.02</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>35.02 total_2026: parent 3,97 != sum(children) 773,20 (2 children)</t>
+          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>42.02</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>61.02.05</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>42.02 total_2026: parent 11,42 != sum(children) 361,07 (2 children)</t>
+          <t>name mismatch vs nomenclator (52%): '*Protectia civila' vs 'Protectie civila si protectia contra inc'</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>42.02</t>
+        <v>5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (55%): 'SUBVENTII PENTRU INVESTITII' vs 'Subventii de la bugetul de stat'</t>
+          <t>unparseable cell '7,726 1,371' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>42.02.69</t>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Sume BS cofinantare proiecte UE 2014-202' vs 'Subvenţii de la bugetul de stat către bu'</t>
+          <t>66.02 total_2026: parent 11,96 != sum(children) 11,93 (1 children)</t>
         </is>
       </c>
     </row>
@@ -34892,23 +34823,23 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>42.02.93</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (36%): 'Sume BS cofinantare proiecte UE 2021-202' vs 'Subvenţii de la bugetul de stat necesare'</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -34917,16 +34848,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.02</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (50%): 'SUME DE PRIMIT DE LA UE 2021-2027' vs 'Sume primite de la UE/alti donatori în c'</t>
+          <t>duplicate of p6 with different values</t>
         </is>
       </c>
     </row>
@@ -34942,7 +34873,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -34958,55 +34889,55 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>54.02</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>67.02.05.01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>54.02 total_2026: parent 6,14 != sum(children) 2,30 (2 children)</t>
+          <t>name mismatch vs nomenclator (28%): '*Alte servicii culturale *Sport' vs 'Sport'</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>duplicate of p5 with different values</t>
+          <t>68.02 total_2026: parent 65,38 != sum(children) 37,54 (3 children)</t>
         </is>
       </c>
     </row>
@@ -35022,7 +34953,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -35031,7 +34962,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -35047,16 +34978,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>68.02.06</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (25%): 'Dobanzi' vs 'Tranzactii privind datoria publica si im'</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Asistenta sociala pentru familie si copi'</t>
         </is>
       </c>
     </row>
@@ -35072,11 +35003,11 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -35086,32 +35017,37 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.02 total_2026: parent 11,40 != sum(children) 250,00 (1 children)</t>
+          <t>70.02 total_2026: parent 65,48 != sum(children) 47,06 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>74.02 total_2026: parent 46,89 != sum(children) 491,34 (3 children)</t>
         </is>
       </c>
     </row>
@@ -35127,71 +35063,66 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>61.02.05</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (52%): '*Protectia civila' vs 'Protectie civila si protectia contra inc'</t>
+          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+        <v>7</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>81</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>unparseable cell '7,726 1,371' in column total_2026</t>
+          <t>name mismatch vs nomenclator (38%): 'operatiuni financiare' vs 'TITLUL XX RAMBURSARI DE CREDITE'</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>66.02 total_2026: parent 11,96 != sum(children) 11,93 (1 children)</t>
+          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -35207,23 +35138,23 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (41%): 'participare la capitalul social al socie' vs 'TITLUL XVII ACTIVE FINANCIARE'</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -35232,16 +35163,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>duplicate of p6 with different values</t>
+          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
         </is>
       </c>
     </row>
@@ -35257,16 +35188,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (41%): 'participare la capitalul social al socie' vs 'TITLUL XVII ACTIVE FINANCIARE'</t>
         </is>
       </c>
     </row>
@@ -35282,46 +35213,41 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>67.02.05.01</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): '*Alte servicii culturale *Sport' vs 'Sport'</t>
+          <t>name mismatch vs nomenclator (27%): 'Cap. 55.02 Dobanzi' vs 'Tranzactii privind datoria publica si im'</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>68.02 total_2026: parent 65,38 != sum(children) 37,54 (3 children)</t>
+          <t>name mismatch vs nomenclator (33%): 'alte drepturi sociale' vs 'TITLUL II  BUNURI SI SERVICII'</t>
         </is>
       </c>
     </row>
@@ -35337,16 +35263,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (44%): 'varsaminte la bugetul de stat aferent pe' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
@@ -35362,76 +35288,66 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>68.02.06</t>
+          <t>45.02</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Asistenta sociala pentru familie si copi'</t>
+          <t>name mismatch vs nomenclator (18%): 'investitii' vs 'Sume primite de la UE/alti donatori în c'</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>70.02 total_2026: parent 65,48 != sum(children) 47,06 (1 children)</t>
+          <t>name mismatch vs nomenclator (26%): '(materiale dendrologice, ingrasaminte, u' vs 'Alte impozite si taxe generale pe bunuri'</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>total_2026</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>74.02 total_2026: parent 46,89 != sum(children) 491,34 (3 children)</t>
+          <t>name mismatch vs nomenclator (35%): 'iluminat public' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
@@ -35447,16 +35363,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (28%): 'cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (39%): 'materiale intretinere iluminat' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
         </is>
       </c>
     </row>
@@ -35472,16 +35388,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (38%): 'operatiuni financiare' vs 'TITLUL XX RAMBURSARI DE CREDITE'</t>
+          <t>name mismatch vs nomenclator (0%): '210.00' vs 'Taxe pe servicii specifice'</t>
         </is>
       </c>
     </row>
@@ -35497,16 +35413,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>name mismatch vs nomenclator (0%): '158.00' vs 'Partea I-a SERVICII PUBLICE GENERALE'</t>
         </is>
       </c>
     </row>
@@ -35522,23 +35438,23 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (41%): 'participare la capitalul social al socie' vs 'TITLUL XVII ACTIVE FINANCIARE'</t>
+          <t>name mismatch vs nomenclator (0%): '50.00' vs 'Partea I-a SERVICII PUBLICE GENERALE'</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -35547,16 +35463,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): '_cheltuieli de capital' vs 'TITLUL XVI ACTIVE NEFINANCIARE (71.01+71'</t>
+          <t>duplicate of p13 with different values</t>
         </is>
       </c>
     </row>
@@ -35572,266 +35488,266 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (41%): 'participare la capitalul social al socie' vs 'TITLUL XVII ACTIVE FINANCIARE'</t>
+          <t>name mismatch vs nomenclator (0%): '138.00' vs 'Tranzactii privind datoria publica si im'</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>55.02</t>
+        <v>14</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (27%): 'Cap. 55.02 Dobanzi' vs 'Tranzactii privind datoria publica si im'</t>
+          <t>unparseable cell '9Scoala Gimnaziala nr.3' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>20</t>
+        <v>14</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>trim2</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'alte drepturi sociale' vs 'TITLUL II  BUNURI SI SERVICII'</t>
+          <t>unparseable cell '9.0.0' in column trim2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>11</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>10</t>
+        <v>17</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (44%): 'varsaminte la bugetul de stat aferent pe' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>unparseable cell '一' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>11</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>45.02</t>
+        <v>17</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'investitii' vs 'Sume primite de la UE/alti donatori în c'</t>
+          <t>unparseable cell 'A' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>11</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>12.02</t>
+        <v>17</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (26%): '(materiale dendrologice, ingrasaminte, u' vs 'Alte impozite si taxe generale pe bunuri'</t>
+          <t>unparseable cell 'B' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>11</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>10</t>
+        <v>17</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (35%): 'iluminat public' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>unparseable cell 'C' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>11</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>10</t>
+        <v>17</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (39%): 'materiale intretinere iluminat' vs 'TITLUL I  CHELTUIELI DE PERSONAL'</t>
+          <t>unparseable cell 'D' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>13</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>15.02</t>
+        <v>17</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '210.00' vs 'Taxe pe servicii specifice'</t>
+          <t>unparseable cell 'II' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>13</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>50.02</t>
+        <v>17</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '158.00' vs 'Partea I-a SERVICII PUBLICE GENERALE'</t>
+          <t>unparseable cell 'ⅢII' in column total_2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>13</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>50.02</t>
+        <v>17</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '50.00' vs 'Partea I-a SERVICII PUBLICE GENERALE'</t>
+          <t>unparseable cell 'a' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -35841,22 +35757,22 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>13</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>50.02</t>
+        <v>17</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>total_2026</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>duplicate of p13 with different values</t>
+          <t>unparseable cell 'b' in column total_2026</t>
         </is>
       </c>
     </row>
@@ -35872,314 +35788,14 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>70.02.07</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '138.00' vs 'Tranzactii privind datoria publica si im'</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>14</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>unparseable cell '9Scoala Gimnaziala nr.3' in column total_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>14</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>trim2</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>unparseable cell '9.0.0' in column trim2</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>17</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>unparseable cell '一' in column total_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>17</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>unparseable cell 'A' in column total_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>17</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>unparseable cell 'B' in column total_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>17</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>unparseable cell 'C' in column total_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>17</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>unparseable cell 'D' in column total_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>17</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>unparseable cell 'II' in column total_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>17</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>unparseable cell 'ⅢII' in column total_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>17</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>unparseable cell 'a' in column total_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>17</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>total_2026</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>unparseable cell 'b' in column total_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>19</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>70.02.07</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
         <is>
           <t>name mismatch vs nomenclator (46%): 'LOCUINTE ŞI DEZVOLTARE PUBLICÃ, LOCUINTE' vs 'Alimantare cu gaze naturale in localitat'</t>
         </is>
@@ -36196,7 +35812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -36218,106 +35834,276 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>229</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>184</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>46</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Modele LLM folosite</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>gemini-3.6-flash</t>
-        </is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>80.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>— Anexa (de la pagina 1)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>local, pag. 1-19, 632 linii</t>
-        </is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>233</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>— BUGETUL LOCAL PROIECT I - C</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>local, pag. 20-29, 378 linii</t>
-        </is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>189</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>81.09999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>80.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1004d751ebe4384fe005ad91</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>7fe6897b4a6290a662d2112c1e04ecd2f5fce33fad1086238c8a45182546cab1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Modele LLM folosite</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>gemini-3.6-flash</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>— Anexa (de la pagina 1)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>local, pag. 1-19, 632 linii</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>— BUGETUL LOCAL PROIECT I - C</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>local, pag. 20-29, 376 linii</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>— BUGETUL CREDITELOR INTERNE PRIMAR, C</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>credite_interne, pag. 30-30, 5 linii</t>
         </is>
